--- a/research/traditional_assets/database/data/united_kingdom/united_kingdom_information_services.xlsx
+++ b/research/traditional_assets/database/data/united_kingdom/united_kingdom_information_services.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09808485433821378</v>
+        <v>0.09787339220236824</v>
       </c>
       <c r="C2">
-        <v>855.5503800941037</v>
+        <v>848.0381049222764</v>
       </c>
       <c r="D2">
-        <v>667.6503800941038</v>
+        <v>669.6581049222764</v>
       </c>
       <c r="E2">
-        <v>-654.8</v>
+        <v>-645.28</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>9.52</v>
       </c>
       <c r="G2">
         <v>187.9</v>
@@ -1445,28 +1445,28 @@
         <v>151.69</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.4788559999999999</v>
       </c>
       <c r="N2">
-        <v>151.69</v>
+        <v>151.211144</v>
       </c>
       <c r="O2">
-        <v>37.9225</v>
+        <v>37.802786</v>
       </c>
       <c r="P2">
-        <v>113.7675</v>
+        <v>113.408358</v>
       </c>
       <c r="Q2">
-        <v>119.5775</v>
+        <v>119.218358</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09808485433821378</v>
+        <v>0.09848095171956388</v>
       </c>
       <c r="T2">
-        <v>1.01912912879999</v>
+        <v>1.026849804018171</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>316.7758156940709</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09787339220236824</v>
+        <v>0.09766193006652271</v>
       </c>
       <c r="C3">
-        <v>848.0381049222764</v>
+        <v>840.537941230847</v>
       </c>
       <c r="D3">
-        <v>669.6581049222764</v>
+        <v>671.677941230847</v>
       </c>
       <c r="E3">
-        <v>-645.28</v>
+        <v>-635.76</v>
       </c>
       <c r="F3">
-        <v>9.52</v>
+        <v>19.04</v>
       </c>
       <c r="G3">
         <v>187.9</v>
@@ -1527,28 +1527,28 @@
         <v>151.69</v>
       </c>
       <c r="M3">
-        <v>0.4788559999999999</v>
+        <v>0.9577119999999999</v>
       </c>
       <c r="N3">
-        <v>151.211144</v>
+        <v>150.732288</v>
       </c>
       <c r="O3">
-        <v>37.802786</v>
+        <v>37.683072</v>
       </c>
       <c r="P3">
-        <v>113.408358</v>
+        <v>113.049216</v>
       </c>
       <c r="Q3">
-        <v>119.218358</v>
+        <v>118.859216</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09848095171956388</v>
+        <v>0.09888513272094154</v>
       </c>
       <c r="T3">
-        <v>1.026849804018171</v>
+        <v>1.034728044036724</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>316.7758156940709</v>
+        <v>158.3879078470355</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09766193006652271</v>
+        <v>0.09745046793067716</v>
       </c>
       <c r="C4">
-        <v>840.537941230847</v>
+        <v>833.0499989440472</v>
       </c>
       <c r="D4">
-        <v>671.677941230847</v>
+        <v>673.7099989440471</v>
       </c>
       <c r="E4">
-        <v>-635.76</v>
+        <v>-626.24</v>
       </c>
       <c r="F4">
-        <v>19.04</v>
+        <v>28.56</v>
       </c>
       <c r="G4">
         <v>187.9</v>
@@ -1609,28 +1609,28 @@
         <v>151.69</v>
       </c>
       <c r="M4">
-        <v>0.9577119999999999</v>
+        <v>1.436568</v>
       </c>
       <c r="N4">
-        <v>150.732288</v>
+        <v>150.253432</v>
       </c>
       <c r="O4">
-        <v>37.683072</v>
+        <v>37.563358</v>
       </c>
       <c r="P4">
-        <v>113.049216</v>
+        <v>112.690074</v>
       </c>
       <c r="Q4">
-        <v>118.859216</v>
+        <v>118.500074</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09888513272094154</v>
+        <v>0.09929764735121357</v>
       </c>
       <c r="T4">
-        <v>1.034728044036724</v>
+        <v>1.042768721993804</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>158.3879078470355</v>
+        <v>105.5919385646903</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09745046793067716</v>
+        <v>0.09723900579483163</v>
       </c>
       <c r="C5">
-        <v>833.0499989440472</v>
+        <v>825.5743893203797</v>
       </c>
       <c r="D5">
-        <v>673.7099989440471</v>
+        <v>675.7543893203798</v>
       </c>
       <c r="E5">
-        <v>-626.24</v>
+        <v>-616.7199999999999</v>
       </c>
       <c r="F5">
-        <v>28.56</v>
+        <v>38.08</v>
       </c>
       <c r="G5">
         <v>187.9</v>
@@ -1691,28 +1691,28 @@
         <v>151.69</v>
       </c>
       <c r="M5">
-        <v>1.436568</v>
+        <v>1.915424</v>
       </c>
       <c r="N5">
-        <v>150.253432</v>
+        <v>149.774576</v>
       </c>
       <c r="O5">
-        <v>37.563358</v>
+        <v>37.443644</v>
       </c>
       <c r="P5">
-        <v>112.690074</v>
+        <v>112.330932</v>
       </c>
       <c r="Q5">
-        <v>118.500074</v>
+        <v>118.140932</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09929764735121357</v>
+        <v>0.09971875603628295</v>
       </c>
       <c r="T5">
-        <v>1.042768721993804</v>
+        <v>1.050976914074989</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>105.5919385646903</v>
+        <v>79.19395392351773</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09723900579483163</v>
+        <v>0.0970275436589861</v>
       </c>
       <c r="C6">
-        <v>825.5743893203797</v>
+        <v>818.1112249729259</v>
       </c>
       <c r="D6">
-        <v>675.7543893203798</v>
+        <v>677.811224972926</v>
       </c>
       <c r="E6">
-        <v>-616.7199999999999</v>
+        <v>-607.1999999999999</v>
       </c>
       <c r="F6">
-        <v>38.08</v>
+        <v>47.6</v>
       </c>
       <c r="G6">
         <v>187.9</v>
@@ -1773,28 +1773,28 @@
         <v>151.69</v>
       </c>
       <c r="M6">
-        <v>1.915424</v>
+        <v>2.39428</v>
       </c>
       <c r="N6">
-        <v>149.774576</v>
+        <v>149.29572</v>
       </c>
       <c r="O6">
-        <v>37.443644</v>
+        <v>37.32393</v>
       </c>
       <c r="P6">
-        <v>112.330932</v>
+        <v>111.97179</v>
       </c>
       <c r="Q6">
-        <v>118.140932</v>
+        <v>117.78179</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09971875603628295</v>
+        <v>0.1001487301673538</v>
       </c>
       <c r="T6">
-        <v>1.050976914074989</v>
+        <v>1.059357910199989</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>79.19395392351773</v>
+        <v>63.35516313881418</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0970275436589861</v>
+        <v>0.09681608152314057</v>
       </c>
       <c r="C7">
-        <v>818.1112249729259</v>
+        <v>810.6606198900218</v>
       </c>
       <c r="D7">
-        <v>677.811224972926</v>
+        <v>679.8806198900219</v>
       </c>
       <c r="E7">
-        <v>-607.1999999999999</v>
+        <v>-597.6799999999999</v>
       </c>
       <c r="F7">
-        <v>47.6</v>
+        <v>57.12</v>
       </c>
       <c r="G7">
         <v>187.9</v>
@@ -1855,28 +1855,28 @@
         <v>151.69</v>
       </c>
       <c r="M7">
-        <v>2.39428</v>
+        <v>2.873136</v>
       </c>
       <c r="N7">
-        <v>149.29572</v>
+        <v>148.816864</v>
       </c>
       <c r="O7">
-        <v>37.32393</v>
+        <v>37.204216</v>
       </c>
       <c r="P7">
-        <v>111.97179</v>
+        <v>111.612648</v>
       </c>
       <c r="Q7">
-        <v>117.78179</v>
+        <v>117.422648</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1001487301673538</v>
+        <v>0.1005878526841921</v>
       </c>
       <c r="T7">
-        <v>1.059357910199989</v>
+        <v>1.067917225391478</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>63.35516313881418</v>
+        <v>52.79596928234515</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09681608152314057</v>
+        <v>0.09660461938729503</v>
       </c>
       <c r="C8">
-        <v>810.6606198900218</v>
+        <v>803.2226894563182</v>
       </c>
       <c r="D8">
-        <v>679.8806198900219</v>
+        <v>681.9626894563182</v>
       </c>
       <c r="E8">
-        <v>-597.6799999999999</v>
+        <v>-588.16</v>
       </c>
       <c r="F8">
-        <v>57.12</v>
+        <v>66.63999999999999</v>
       </c>
       <c r="G8">
         <v>187.9</v>
@@ -1937,28 +1937,28 @@
         <v>151.69</v>
       </c>
       <c r="M8">
-        <v>2.873136</v>
+        <v>3.351991999999999</v>
       </c>
       <c r="N8">
-        <v>148.816864</v>
+        <v>148.338008</v>
       </c>
       <c r="O8">
-        <v>37.204216</v>
+        <v>37.084502</v>
       </c>
       <c r="P8">
-        <v>111.612648</v>
+        <v>111.253506</v>
       </c>
       <c r="Q8">
-        <v>117.422648</v>
+        <v>117.063506</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1005878526841921</v>
+        <v>0.1010364186960162</v>
       </c>
       <c r="T8">
-        <v>1.067917225391478</v>
+        <v>1.076660611877408</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>52.79596928234515</v>
+        <v>45.25368795629585</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09660461938729502</v>
+        <v>0.09639315725144951</v>
       </c>
       <c r="C9">
-        <v>803.2226894563182</v>
+        <v>795.7975504742242</v>
       </c>
       <c r="D9">
-        <v>681.9626894563182</v>
+        <v>684.0575504742242</v>
       </c>
       <c r="E9">
-        <v>-588.16</v>
+        <v>-578.64</v>
       </c>
       <c r="F9">
-        <v>66.64</v>
+        <v>76.16</v>
       </c>
       <c r="G9">
         <v>187.9</v>
@@ -2019,28 +2019,28 @@
         <v>151.69</v>
       </c>
       <c r="M9">
-        <v>3.351992</v>
+        <v>3.830848</v>
       </c>
       <c r="N9">
-        <v>148.338008</v>
+        <v>147.859152</v>
       </c>
       <c r="O9">
-        <v>37.084502</v>
+        <v>36.964788</v>
       </c>
       <c r="P9">
-        <v>111.253506</v>
+        <v>110.894364</v>
       </c>
       <c r="Q9">
-        <v>117.063506</v>
+        <v>116.704364</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1010364186960162</v>
+        <v>0.1014947361428799</v>
       </c>
       <c r="T9">
-        <v>1.076660611877408</v>
+        <v>1.085594071982598</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>45.25368795629583</v>
+        <v>39.59697696175886</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09639315725144951</v>
+        <v>0.09618169511560397</v>
       </c>
       <c r="C10">
-        <v>795.7975504742242</v>
+        <v>788.3853211857527</v>
       </c>
       <c r="D10">
-        <v>684.0575504742242</v>
+        <v>686.1653211857526</v>
       </c>
       <c r="E10">
-        <v>-578.64</v>
+        <v>-569.12</v>
       </c>
       <c r="F10">
-        <v>76.16</v>
+        <v>85.67999999999999</v>
       </c>
       <c r="G10">
         <v>187.9</v>
@@ -2101,28 +2101,28 @@
         <v>151.69</v>
       </c>
       <c r="M10">
-        <v>3.830848</v>
+        <v>4.309703999999999</v>
       </c>
       <c r="N10">
-        <v>147.859152</v>
+        <v>147.380296</v>
       </c>
       <c r="O10">
-        <v>36.964788</v>
+        <v>36.845074</v>
       </c>
       <c r="P10">
-        <v>110.894364</v>
+        <v>110.535222</v>
       </c>
       <c r="Q10">
-        <v>116.704364</v>
+        <v>116.345222</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1014947361428799</v>
+        <v>0.1019631265006637</v>
       </c>
       <c r="T10">
-        <v>1.085594071982598</v>
+        <v>1.094723871870318</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>39.59697696175886</v>
+        <v>35.19731285489677</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09618169511560397</v>
+        <v>0.09597023297975843</v>
       </c>
       <c r="C11">
-        <v>788.3853211857527</v>
+        <v>780.9861212947651</v>
       </c>
       <c r="D11">
-        <v>686.1653211857526</v>
+        <v>688.2861212947652</v>
       </c>
       <c r="E11">
-        <v>-569.12</v>
+        <v>-559.5999999999999</v>
       </c>
       <c r="F11">
-        <v>85.67999999999999</v>
+        <v>95.19999999999999</v>
       </c>
       <c r="G11">
         <v>187.9</v>
@@ -2183,28 +2183,28 @@
         <v>151.69</v>
       </c>
       <c r="M11">
-        <v>4.309703999999999</v>
+        <v>4.788559999999999</v>
       </c>
       <c r="N11">
-        <v>147.380296</v>
+        <v>146.90144</v>
       </c>
       <c r="O11">
-        <v>36.845074</v>
+        <v>36.72536</v>
       </c>
       <c r="P11">
-        <v>110.535222</v>
+        <v>110.17608</v>
       </c>
       <c r="Q11">
-        <v>116.345222</v>
+        <v>115.98608</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1019631265006637</v>
+        <v>0.1024419255330649</v>
       </c>
       <c r="T11">
-        <v>1.094723871870318</v>
+        <v>1.104056556199989</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>35.19731285489677</v>
+        <v>31.67758156940709</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09597023297975843</v>
+        <v>0.09575877084391289</v>
       </c>
       <c r="C12">
-        <v>780.9861212947651</v>
+        <v>773.6000719896351</v>
       </c>
       <c r="D12">
-        <v>688.2861212947652</v>
+        <v>690.4200719896352</v>
       </c>
       <c r="E12">
-        <v>-559.5999999999999</v>
+        <v>-550.0799999999999</v>
       </c>
       <c r="F12">
-        <v>95.2</v>
+        <v>104.72</v>
       </c>
       <c r="G12">
         <v>187.9</v>
@@ -2265,28 +2265,28 @@
         <v>151.69</v>
       </c>
       <c r="M12">
-        <v>4.788559999999999</v>
+        <v>5.267416</v>
       </c>
       <c r="N12">
-        <v>146.90144</v>
+        <v>146.422584</v>
       </c>
       <c r="O12">
-        <v>36.72536</v>
+        <v>36.605646</v>
       </c>
       <c r="P12">
-        <v>110.17608</v>
+        <v>109.816938</v>
       </c>
       <c r="Q12">
-        <v>115.98608</v>
+        <v>115.626938</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1024419255330649</v>
+        <v>0.1029314840942842</v>
       </c>
       <c r="T12">
-        <v>1.104056556199989</v>
+        <v>1.113598963773022</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>31.67758156940709</v>
+        <v>28.79780142673372</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09575877084391289</v>
+        <v>0.09554730870806737</v>
       </c>
       <c r="C13">
-        <v>773.6000719896351</v>
+        <v>766.2272959663316</v>
       </c>
       <c r="D13">
-        <v>690.4200719896352</v>
+        <v>692.5672959663316</v>
       </c>
       <c r="E13">
-        <v>-550.0799999999999</v>
+        <v>-540.5599999999999</v>
       </c>
       <c r="F13">
-        <v>104.72</v>
+        <v>114.24</v>
       </c>
       <c r="G13">
         <v>187.9</v>
@@ -2347,28 +2347,28 @@
         <v>151.69</v>
       </c>
       <c r="M13">
-        <v>5.267416</v>
+        <v>5.746271999999999</v>
       </c>
       <c r="N13">
-        <v>146.422584</v>
+        <v>145.943728</v>
       </c>
       <c r="O13">
-        <v>36.605646</v>
+        <v>36.485932</v>
       </c>
       <c r="P13">
-        <v>109.816938</v>
+        <v>109.457796</v>
       </c>
       <c r="Q13">
-        <v>115.626938</v>
+        <v>115.267796</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1029314840942842</v>
+        <v>0.1034321689864402</v>
       </c>
       <c r="T13">
-        <v>1.113598963773022</v>
+        <v>1.123358244245443</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>28.79780142673372</v>
+        <v>26.39798464117257</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09554730870806737</v>
+        <v>0.09533584657222183</v>
       </c>
       <c r="C14">
-        <v>766.2272959663316</v>
+        <v>758.8679174519359</v>
       </c>
       <c r="D14">
-        <v>692.5672959663316</v>
+        <v>694.7279174519359</v>
       </c>
       <c r="E14">
-        <v>-540.5599999999999</v>
+        <v>-531.04</v>
       </c>
       <c r="F14">
-        <v>114.24</v>
+        <v>123.76</v>
       </c>
       <c r="G14">
         <v>187.9</v>
@@ -2429,28 +2429,28 @@
         <v>151.69</v>
       </c>
       <c r="M14">
-        <v>5.746271999999999</v>
+        <v>6.225128</v>
       </c>
       <c r="N14">
-        <v>145.943728</v>
+        <v>145.464872</v>
       </c>
       <c r="O14">
-        <v>36.485932</v>
+        <v>36.366218</v>
       </c>
       <c r="P14">
-        <v>109.457796</v>
+        <v>109.098654</v>
       </c>
       <c r="Q14">
-        <v>115.267796</v>
+        <v>114.908654</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1034321689864402</v>
+        <v>0.103944363876117</v>
       </c>
       <c r="T14">
-        <v>1.123358244245443</v>
+        <v>1.133341875993092</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>26.39798464117257</v>
+        <v>24.36737043800545</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09533584657222183</v>
+        <v>0.09512438443637627</v>
       </c>
       <c r="C15">
-        <v>758.8679174519359</v>
+        <v>751.5220622285993</v>
       </c>
       <c r="D15">
-        <v>694.7279174519359</v>
+        <v>696.9020622285993</v>
       </c>
       <c r="E15">
-        <v>-531.04</v>
+        <v>-521.52</v>
       </c>
       <c r="F15">
-        <v>123.76</v>
+        <v>133.28</v>
       </c>
       <c r="G15">
         <v>187.9</v>
@@ -2511,28 +2511,28 @@
         <v>151.69</v>
       </c>
       <c r="M15">
-        <v>6.225128</v>
+        <v>6.703984</v>
       </c>
       <c r="N15">
-        <v>145.464872</v>
+        <v>144.986016</v>
       </c>
       <c r="O15">
-        <v>36.366218</v>
+        <v>36.246504</v>
       </c>
       <c r="P15">
-        <v>109.098654</v>
+        <v>108.739512</v>
       </c>
       <c r="Q15">
-        <v>114.908654</v>
+        <v>114.549512</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.103944363876117</v>
+        <v>0.1044684702748561</v>
       </c>
       <c r="T15">
-        <v>1.133341875993092</v>
+        <v>1.143557685223244</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>24.36737043800545</v>
+        <v>22.62684397814792</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09512438443637627</v>
+        <v>0.09491292230053076</v>
       </c>
       <c r="C16">
-        <v>751.5220622285993</v>
+        <v>744.1898576579522</v>
       </c>
       <c r="D16">
-        <v>696.9020622285993</v>
+        <v>699.0898576579522</v>
       </c>
       <c r="E16">
-        <v>-521.52</v>
+        <v>-511.9999999999999</v>
       </c>
       <c r="F16">
-        <v>133.28</v>
+        <v>142.8</v>
       </c>
       <c r="G16">
         <v>187.9</v>
@@ -2593,28 +2593,28 @@
         <v>151.69</v>
       </c>
       <c r="M16">
-        <v>6.703984</v>
+        <v>7.182840000000001</v>
       </c>
       <c r="N16">
-        <v>144.986016</v>
+        <v>144.50716</v>
       </c>
       <c r="O16">
-        <v>36.246504</v>
+        <v>36.12679</v>
       </c>
       <c r="P16">
-        <v>108.739512</v>
+        <v>108.38037</v>
       </c>
       <c r="Q16">
-        <v>114.549512</v>
+        <v>114.19037</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1044684702748561</v>
+        <v>0.1050049085888597</v>
       </c>
       <c r="T16">
-        <v>1.143557685223244</v>
+        <v>1.154013866435282</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>22.62684397814792</v>
+        <v>21.11838771293806</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09491292230053076</v>
+        <v>0.09470146016468521</v>
       </c>
       <c r="C17">
-        <v>744.1898576579522</v>
+        <v>736.8714327059758</v>
       </c>
       <c r="D17">
-        <v>699.0898576579522</v>
+        <v>701.2914327059759</v>
       </c>
       <c r="E17">
-        <v>-512</v>
+        <v>-502.48</v>
       </c>
       <c r="F17">
-        <v>142.8</v>
+        <v>152.32</v>
       </c>
       <c r="G17">
         <v>187.9</v>
@@ -2675,28 +2675,28 @@
         <v>151.69</v>
       </c>
       <c r="M17">
-        <v>7.182839999999999</v>
+        <v>7.661695999999999</v>
       </c>
       <c r="N17">
-        <v>144.50716</v>
+        <v>144.028304</v>
       </c>
       <c r="O17">
-        <v>36.12679</v>
+        <v>36.007076</v>
       </c>
       <c r="P17">
-        <v>108.38037</v>
+        <v>108.021228</v>
       </c>
       <c r="Q17">
-        <v>114.19037</v>
+        <v>113.831228</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1050049085888597</v>
+        <v>0.1055541192436729</v>
       </c>
       <c r="T17">
-        <v>1.154013866435282</v>
+        <v>1.164719004342845</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>21.11838771293806</v>
+        <v>19.79848848087943</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09470146016468521</v>
+        <v>0.09448999802883967</v>
       </c>
       <c r="C18">
-        <v>736.8714327059758</v>
+        <v>729.5669179683423</v>
       </c>
       <c r="D18">
-        <v>701.2914327059759</v>
+        <v>703.5069179683423</v>
       </c>
       <c r="E18">
-        <v>-502.48</v>
+        <v>-492.9599999999999</v>
       </c>
       <c r="F18">
-        <v>152.32</v>
+        <v>161.84</v>
       </c>
       <c r="G18">
         <v>187.9</v>
@@ -2757,28 +2757,28 @@
         <v>151.69</v>
       </c>
       <c r="M18">
-        <v>7.661695999999999</v>
+        <v>8.140552</v>
       </c>
       <c r="N18">
-        <v>144.028304</v>
+        <v>143.549448</v>
       </c>
       <c r="O18">
-        <v>36.007076</v>
+        <v>35.887362</v>
       </c>
       <c r="P18">
-        <v>108.021228</v>
+        <v>107.662086</v>
       </c>
       <c r="Q18">
-        <v>113.831228</v>
+        <v>113.472086</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1055541192436729</v>
+        <v>0.1061165638901683</v>
       </c>
       <c r="T18">
-        <v>1.164719004342845</v>
+        <v>1.175682097380711</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>19.79848848087943</v>
+        <v>18.63387151141593</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09448999802883967</v>
+        <v>0.09427853589299416</v>
       </c>
       <c r="C19">
-        <v>729.5669179683423</v>
+        <v>722.2764456962394</v>
       </c>
       <c r="D19">
-        <v>703.5069179683423</v>
+        <v>705.7364456962395</v>
       </c>
       <c r="E19">
-        <v>-492.9599999999999</v>
+        <v>-483.4399999999999</v>
       </c>
       <c r="F19">
-        <v>161.84</v>
+        <v>171.36</v>
       </c>
       <c r="G19">
         <v>187.9</v>
@@ -2839,28 +2839,28 @@
         <v>151.69</v>
       </c>
       <c r="M19">
-        <v>8.140552</v>
+        <v>8.619408</v>
       </c>
       <c r="N19">
-        <v>143.549448</v>
+        <v>143.070592</v>
       </c>
       <c r="O19">
-        <v>35.887362</v>
+        <v>35.767648</v>
       </c>
       <c r="P19">
-        <v>107.662086</v>
+        <v>107.302944</v>
       </c>
       <c r="Q19">
-        <v>113.472086</v>
+        <v>113.112944</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1061165638901683</v>
+        <v>0.1066927266987734</v>
       </c>
       <c r="T19">
-        <v>1.175682097380711</v>
+        <v>1.186912582931695</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>18.63387151141593</v>
+        <v>17.59865642744838</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09427853589299416</v>
+        <v>0.09406707375714862</v>
       </c>
       <c r="C20">
-        <v>722.2764456962394</v>
+        <v>715.0001498226881</v>
       </c>
       <c r="D20">
-        <v>705.7364456962395</v>
+        <v>707.9801498226881</v>
       </c>
       <c r="E20">
-        <v>-483.4399999999999</v>
+        <v>-473.92</v>
       </c>
       <c r="F20">
-        <v>171.36</v>
+        <v>180.88</v>
       </c>
       <c r="G20">
         <v>187.9</v>
@@ -2921,28 +2921,28 @@
         <v>151.69</v>
       </c>
       <c r="M20">
-        <v>8.619407999999998</v>
+        <v>9.098263999999999</v>
       </c>
       <c r="N20">
-        <v>143.070592</v>
+        <v>142.591736</v>
       </c>
       <c r="O20">
-        <v>35.767648</v>
+        <v>35.647934</v>
       </c>
       <c r="P20">
-        <v>107.302944</v>
+        <v>106.943802</v>
       </c>
       <c r="Q20">
-        <v>113.112944</v>
+        <v>112.753802</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1066927266987734</v>
+        <v>0.1072831157495662</v>
       </c>
       <c r="T20">
-        <v>1.186912582931695</v>
+        <v>1.19842036442221</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>17.59865642744839</v>
+        <v>16.67241135231952</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09406707375714862</v>
+        <v>0.0938556116213031</v>
       </c>
       <c r="C21">
-        <v>715.0001498226881</v>
+        <v>707.7381659893596</v>
       </c>
       <c r="D21">
-        <v>707.9801498226881</v>
+        <v>710.2381659893596</v>
       </c>
       <c r="E21">
-        <v>-473.92</v>
+        <v>-464.4</v>
       </c>
       <c r="F21">
-        <v>180.88</v>
+        <v>190.4</v>
       </c>
       <c r="G21">
         <v>187.9</v>
@@ -3003,28 +3003,28 @@
         <v>151.69</v>
       </c>
       <c r="M21">
-        <v>9.098263999999999</v>
+        <v>9.577119999999999</v>
       </c>
       <c r="N21">
-        <v>142.591736</v>
+        <v>142.11288</v>
       </c>
       <c r="O21">
-        <v>35.647934</v>
+        <v>35.52822</v>
       </c>
       <c r="P21">
-        <v>106.943802</v>
+        <v>106.58466</v>
       </c>
       <c r="Q21">
-        <v>112.753802</v>
+        <v>112.39466</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1072831157495662</v>
+        <v>0.1078882645266289</v>
       </c>
       <c r="T21">
-        <v>1.19842036442221</v>
+        <v>1.210215840449988</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>16.67241135231952</v>
+        <v>15.83879078470354</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0938556116213031</v>
+        <v>0.09364414948545756</v>
       </c>
       <c r="C22">
-        <v>707.7381659893596</v>
+        <v>700.4906315739136</v>
       </c>
       <c r="D22">
-        <v>710.2381659893596</v>
+        <v>712.5106315739137</v>
       </c>
       <c r="E22">
-        <v>-464.4</v>
+        <v>-454.8799999999999</v>
       </c>
       <c r="F22">
-        <v>190.4</v>
+        <v>199.92</v>
       </c>
       <c r="G22">
         <v>187.9</v>
@@ -3085,28 +3085,28 @@
         <v>151.69</v>
       </c>
       <c r="M22">
-        <v>9.577119999999999</v>
+        <v>10.055976</v>
       </c>
       <c r="N22">
-        <v>142.11288</v>
+        <v>141.634024</v>
       </c>
       <c r="O22">
-        <v>35.52822</v>
+        <v>35.408506</v>
       </c>
       <c r="P22">
-        <v>106.58466</v>
+        <v>106.225518</v>
       </c>
       <c r="Q22">
-        <v>112.39466</v>
+        <v>112.035518</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1078882645266289</v>
+        <v>0.1085087335258956</v>
       </c>
       <c r="T22">
-        <v>1.210215840449988</v>
+        <v>1.222309936124038</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>15.83879078470354</v>
+        <v>15.08456265209861</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09364414948545755</v>
+        <v>0.09343268734961201</v>
       </c>
       <c r="C23">
-        <v>700.4906315739137</v>
+        <v>693.2576857178569</v>
       </c>
       <c r="D23">
-        <v>712.5106315739137</v>
+        <v>714.797685717857</v>
       </c>
       <c r="E23">
-        <v>-454.88</v>
+        <v>-445.36</v>
       </c>
       <c r="F23">
-        <v>199.92</v>
+        <v>209.44</v>
       </c>
       <c r="G23">
         <v>187.9</v>
@@ -3167,28 +3167,28 @@
         <v>151.69</v>
       </c>
       <c r="M23">
-        <v>10.055976</v>
+        <v>10.534832</v>
       </c>
       <c r="N23">
-        <v>141.634024</v>
+        <v>141.155168</v>
       </c>
       <c r="O23">
-        <v>35.408506</v>
+        <v>35.288792</v>
       </c>
       <c r="P23">
-        <v>106.225518</v>
+        <v>105.866376</v>
       </c>
       <c r="Q23">
-        <v>112.035518</v>
+        <v>111.676376</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1085087335258956</v>
+        <v>0.1091451119866821</v>
       </c>
       <c r="T23">
-        <v>1.222309936124038</v>
+        <v>1.234714136815372</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>15.08456265209862</v>
+        <v>14.39890071336686</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09343268734961201</v>
+        <v>0.09322122521376647</v>
       </c>
       <c r="C24">
-        <v>693.2576857178569</v>
+        <v>686.0394693549445</v>
       </c>
       <c r="D24">
-        <v>714.797685717857</v>
+        <v>717.0994693549445</v>
       </c>
       <c r="E24">
-        <v>-445.36</v>
+        <v>-435.8399999999999</v>
       </c>
       <c r="F24">
-        <v>209.44</v>
+        <v>218.96</v>
       </c>
       <c r="G24">
         <v>187.9</v>
@@ -3249,28 +3249,28 @@
         <v>151.69</v>
       </c>
       <c r="M24">
-        <v>10.534832</v>
+        <v>11.013688</v>
       </c>
       <c r="N24">
-        <v>141.155168</v>
+        <v>140.676312</v>
       </c>
       <c r="O24">
-        <v>35.288792</v>
+        <v>35.169078</v>
       </c>
       <c r="P24">
-        <v>105.866376</v>
+        <v>105.507234</v>
       </c>
       <c r="Q24">
-        <v>111.676376</v>
+        <v>111.317234</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1091451119866821</v>
+        <v>0.1097980197581383</v>
       </c>
       <c r="T24">
-        <v>1.234714136815372</v>
+        <v>1.247440524537649</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>14.39890071336686</v>
+        <v>13.77286155191612</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09322122521376647</v>
+        <v>0.09300976307792094</v>
       </c>
       <c r="C25">
-        <v>686.0394693549445</v>
+        <v>678.836125240129</v>
       </c>
       <c r="D25">
-        <v>717.0994693549445</v>
+        <v>719.4161252401291</v>
       </c>
       <c r="E25">
-        <v>-435.8399999999999</v>
+        <v>-426.3199999999999</v>
       </c>
       <c r="F25">
-        <v>218.96</v>
+        <v>228.48</v>
       </c>
       <c r="G25">
         <v>187.9</v>
@@ -3331,28 +3331,28 @@
         <v>151.69</v>
       </c>
       <c r="M25">
-        <v>11.013688</v>
+        <v>11.492544</v>
       </c>
       <c r="N25">
-        <v>140.676312</v>
+        <v>140.197456</v>
       </c>
       <c r="O25">
-        <v>35.169078</v>
+        <v>35.049364</v>
       </c>
       <c r="P25">
-        <v>105.507234</v>
+        <v>105.148092</v>
       </c>
       <c r="Q25">
-        <v>111.317234</v>
+        <v>110.958092</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1097980197581383</v>
+        <v>0.1104681093130539</v>
       </c>
       <c r="T25">
-        <v>1.247440524537649</v>
+        <v>1.260501817199987</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>13.77286155191612</v>
+        <v>13.19899232058629</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09300976307792093</v>
+        <v>0.09307955094207541</v>
       </c>
       <c r="C26">
-        <v>678.8361252401291</v>
+        <v>668.5499170322984</v>
       </c>
       <c r="D26">
-        <v>719.4161252401292</v>
+        <v>718.6499170322984</v>
       </c>
       <c r="E26">
-        <v>-426.3199999999999</v>
+        <v>-416.8</v>
       </c>
       <c r="F26">
-        <v>228.48</v>
+        <v>238</v>
       </c>
       <c r="G26">
         <v>187.9</v>
@@ -3413,45 +3413,45 @@
         <v>151.69</v>
       </c>
       <c r="M26">
-        <v>11.492544</v>
+        <v>12.3284</v>
       </c>
       <c r="N26">
-        <v>140.197456</v>
+        <v>139.3616</v>
       </c>
       <c r="O26">
-        <v>35.049364</v>
+        <v>34.8404</v>
       </c>
       <c r="P26">
-        <v>105.148092</v>
+        <v>104.5212</v>
       </c>
       <c r="Q26">
-        <v>110.958092</v>
+        <v>110.3312</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1104681093130539</v>
+        <v>0.1111560679227672</v>
       </c>
       <c r="T26">
-        <v>1.260501817199987</v>
+        <v>1.273911410999987</v>
       </c>
       <c r="U26">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V26">
         <v>0.25</v>
       </c>
       <c r="W26">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y26">
-        <v>13.19899232058629</v>
+        <v>12.3041108335226</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09307955094207541</v>
+        <v>0.09287933880622988</v>
       </c>
       <c r="C27">
-        <v>668.5499170322984</v>
+        <v>661.2324555182051</v>
       </c>
       <c r="D27">
-        <v>718.6499170322984</v>
+        <v>720.8524555182051</v>
       </c>
       <c r="E27">
-        <v>-416.8</v>
+        <v>-407.28</v>
       </c>
       <c r="F27">
-        <v>238</v>
+        <v>247.52</v>
       </c>
       <c r="G27">
         <v>187.9</v>
@@ -3495,28 +3495,28 @@
         <v>151.69</v>
       </c>
       <c r="M27">
-        <v>12.3284</v>
+        <v>12.821536</v>
       </c>
       <c r="N27">
-        <v>139.3616</v>
+        <v>138.868464</v>
       </c>
       <c r="O27">
-        <v>34.8404</v>
+        <v>34.717116</v>
       </c>
       <c r="P27">
-        <v>104.5212</v>
+        <v>104.151348</v>
       </c>
       <c r="Q27">
-        <v>110.3312</v>
+        <v>109.961348</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1111560679227672</v>
+        <v>0.1118626200084188</v>
       </c>
       <c r="T27">
-        <v>1.273911410999987</v>
+        <v>1.287683426254041</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>12.3041108335226</v>
+        <v>11.83087580146404</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09287933880622988</v>
+        <v>0.09267912667038435</v>
       </c>
       <c r="C28">
-        <v>661.2324555182051</v>
+        <v>653.9285363128065</v>
       </c>
       <c r="D28">
-        <v>720.8524555182051</v>
+        <v>723.0685363128066</v>
       </c>
       <c r="E28">
-        <v>-407.28</v>
+        <v>-397.7599999999999</v>
       </c>
       <c r="F28">
-        <v>247.52</v>
+        <v>257.04</v>
       </c>
       <c r="G28">
         <v>187.9</v>
@@ -3577,28 +3577,28 @@
         <v>151.69</v>
       </c>
       <c r="M28">
-        <v>12.821536</v>
+        <v>13.314672</v>
       </c>
       <c r="N28">
-        <v>138.868464</v>
+        <v>138.375328</v>
       </c>
       <c r="O28">
-        <v>34.717116</v>
+        <v>34.593832</v>
       </c>
       <c r="P28">
-        <v>104.151348</v>
+        <v>103.781496</v>
       </c>
       <c r="Q28">
-        <v>109.961348</v>
+        <v>109.591496</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1118626200084188</v>
+        <v>0.112588529685458</v>
       </c>
       <c r="T28">
-        <v>1.287683426254041</v>
+        <v>1.301832756994507</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>11.83087580146404</v>
+        <v>11.39269521622463</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09267912667038435</v>
+        <v>0.09247891453453883</v>
       </c>
       <c r="C29">
-        <v>653.9285363128065</v>
+        <v>646.6382846985873</v>
       </c>
       <c r="D29">
-        <v>723.0685363128066</v>
+        <v>725.2982846985874</v>
       </c>
       <c r="E29">
-        <v>-397.7599999999999</v>
+        <v>-388.24</v>
       </c>
       <c r="F29">
-        <v>257.04</v>
+        <v>266.56</v>
       </c>
       <c r="G29">
         <v>187.9</v>
@@ -3659,28 +3659,28 @@
         <v>151.69</v>
       </c>
       <c r="M29">
-        <v>13.314672</v>
+        <v>13.807808</v>
       </c>
       <c r="N29">
-        <v>138.375328</v>
+        <v>137.882192</v>
       </c>
       <c r="O29">
-        <v>34.593832</v>
+        <v>34.470548</v>
       </c>
       <c r="P29">
-        <v>103.781496</v>
+        <v>103.411644</v>
       </c>
       <c r="Q29">
-        <v>109.591496</v>
+        <v>109.221644</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.112588529685458</v>
+        <v>0.1133346035201928</v>
       </c>
       <c r="T29">
-        <v>1.301832756994507</v>
+        <v>1.316375124699987</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>11.39269521622463</v>
+        <v>10.98581324421661</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09247891453453883</v>
+        <v>0.09227870239869328</v>
       </c>
       <c r="C30">
-        <v>646.6382846985873</v>
+        <v>639.3618275081625</v>
       </c>
       <c r="D30">
-        <v>725.2982846985874</v>
+        <v>727.5418275081626</v>
       </c>
       <c r="E30">
-        <v>-388.24</v>
+        <v>-378.7199999999999</v>
       </c>
       <c r="F30">
-        <v>266.56</v>
+        <v>276.08</v>
       </c>
       <c r="G30">
         <v>187.9</v>
@@ -3741,28 +3741,28 @@
         <v>151.69</v>
       </c>
       <c r="M30">
-        <v>13.807808</v>
+        <v>14.300944</v>
       </c>
       <c r="N30">
-        <v>137.882192</v>
+        <v>137.389056</v>
       </c>
       <c r="O30">
-        <v>34.470548</v>
+        <v>34.347264</v>
       </c>
       <c r="P30">
-        <v>103.411644</v>
+        <v>103.041792</v>
       </c>
       <c r="Q30">
-        <v>109.221644</v>
+        <v>108.851792</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1133346035201928</v>
+        <v>0.1141016935192863</v>
       </c>
       <c r="T30">
-        <v>1.316375124699987</v>
+        <v>1.331327136566183</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>10.98581324421661</v>
+        <v>10.60699209786431</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09227870239869328</v>
+        <v>0.09207849026284773</v>
       </c>
       <c r="C31">
-        <v>639.3618275081626</v>
+        <v>632.0992931483252</v>
       </c>
       <c r="D31">
-        <v>727.5418275081626</v>
+        <v>729.7992931483251</v>
       </c>
       <c r="E31">
-        <v>-378.72</v>
+        <v>-369.2</v>
       </c>
       <c r="F31">
-        <v>276.08</v>
+        <v>285.6</v>
       </c>
       <c r="G31">
         <v>187.9</v>
@@ -3823,28 +3823,28 @@
         <v>151.69</v>
       </c>
       <c r="M31">
-        <v>14.300944</v>
+        <v>14.79408</v>
       </c>
       <c r="N31">
-        <v>137.389056</v>
+        <v>136.89592</v>
       </c>
       <c r="O31">
-        <v>34.347264</v>
+        <v>34.22398</v>
       </c>
       <c r="P31">
-        <v>103.041792</v>
+        <v>102.67194</v>
       </c>
       <c r="Q31">
-        <v>108.851792</v>
+        <v>108.48194</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1141016935192863</v>
+        <v>0.1148907003754968</v>
       </c>
       <c r="T31">
-        <v>1.331327136566183</v>
+        <v>1.346706348771415</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>10.60699209786431</v>
+        <v>10.25342569460217</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09207849026284773</v>
+        <v>0.09187827812700219</v>
       </c>
       <c r="C32">
-        <v>632.0992931483252</v>
+        <v>624.8508116245458</v>
       </c>
       <c r="D32">
-        <v>729.7992931483251</v>
+        <v>732.0708116245459</v>
       </c>
       <c r="E32">
-        <v>-369.2</v>
+        <v>-359.6799999999999</v>
       </c>
       <c r="F32">
-        <v>285.6</v>
+        <v>295.12</v>
       </c>
       <c r="G32">
         <v>187.9</v>
@@ -3905,28 +3905,28 @@
         <v>151.69</v>
       </c>
       <c r="M32">
-        <v>14.79408</v>
+        <v>15.287216</v>
       </c>
       <c r="N32">
-        <v>136.89592</v>
+        <v>136.402784</v>
       </c>
       <c r="O32">
-        <v>34.22398</v>
+        <v>34.100696</v>
       </c>
       <c r="P32">
-        <v>102.67194</v>
+        <v>102.302088</v>
       </c>
       <c r="Q32">
-        <v>108.48194</v>
+        <v>108.112088</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1148907003754968</v>
+        <v>0.1157025769956554</v>
       </c>
       <c r="T32">
-        <v>1.346706348771415</v>
+        <v>1.362531335243464</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>10.25342569460217</v>
+        <v>9.922670027034354</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09187827812700219</v>
+        <v>0.09208606599115668</v>
       </c>
       <c r="C33">
-        <v>624.8508116245458</v>
+        <v>612.9736190334413</v>
       </c>
       <c r="D33">
-        <v>732.0708116245459</v>
+        <v>729.7136190334413</v>
       </c>
       <c r="E33">
-        <v>-359.6799999999999</v>
+        <v>-350.16</v>
       </c>
       <c r="F33">
-        <v>295.12</v>
+        <v>304.64</v>
       </c>
       <c r="G33">
         <v>187.9</v>
@@ -3987,45 +3987,45 @@
         <v>151.69</v>
       </c>
       <c r="M33">
-        <v>15.287216</v>
+        <v>16.29824</v>
       </c>
       <c r="N33">
-        <v>136.402784</v>
+        <v>135.39176</v>
       </c>
       <c r="O33">
-        <v>34.100696</v>
+        <v>33.84794</v>
       </c>
       <c r="P33">
-        <v>102.302088</v>
+        <v>101.54382</v>
       </c>
       <c r="Q33">
-        <v>108.112088</v>
+        <v>107.35382</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1157025769956554</v>
+        <v>0.1165383323399363</v>
       </c>
       <c r="T33">
-        <v>1.362531335243464</v>
+        <v>1.378821762494103</v>
       </c>
       <c r="U33">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V33">
         <v>0.25</v>
       </c>
       <c r="W33">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>9.922670027034354</v>
+        <v>9.307139912039583</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09208606599115668</v>
+        <v>0.09189860385531112</v>
       </c>
       <c r="C34">
-        <v>612.9736190334413</v>
+        <v>605.5795601904622</v>
       </c>
       <c r="D34">
-        <v>729.7136190334413</v>
+        <v>731.8395601904622</v>
       </c>
       <c r="E34">
-        <v>-350.16</v>
+        <v>-340.6399999999999</v>
       </c>
       <c r="F34">
-        <v>304.64</v>
+        <v>314.16</v>
       </c>
       <c r="G34">
         <v>187.9</v>
@@ -4069,28 +4069,28 @@
         <v>151.69</v>
       </c>
       <c r="M34">
-        <v>16.29824</v>
+        <v>16.80756</v>
       </c>
       <c r="N34">
-        <v>135.39176</v>
+        <v>134.88244</v>
       </c>
       <c r="O34">
-        <v>33.84794</v>
+        <v>33.72061</v>
       </c>
       <c r="P34">
-        <v>101.54382</v>
+        <v>101.16183</v>
       </c>
       <c r="Q34">
-        <v>107.35382</v>
+        <v>106.97183</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1165383323399363</v>
+        <v>0.117399035604942</v>
       </c>
       <c r="T34">
-        <v>1.378821762494103</v>
+        <v>1.39559847115521</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>9.307139912039583</v>
+        <v>9.025105369250504</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09189860385531112</v>
+        <v>0.09171114171946559</v>
       </c>
       <c r="C35">
-        <v>605.5795601904622</v>
+        <v>598.1979249383173</v>
       </c>
       <c r="D35">
-        <v>731.8395601904622</v>
+        <v>733.9779249383173</v>
       </c>
       <c r="E35">
-        <v>-340.6399999999999</v>
+        <v>-331.1199999999999</v>
       </c>
       <c r="F35">
-        <v>314.16</v>
+        <v>323.68</v>
       </c>
       <c r="G35">
         <v>187.9</v>
@@ -4151,28 +4151,28 @@
         <v>151.69</v>
       </c>
       <c r="M35">
-        <v>16.80756</v>
+        <v>17.31688</v>
       </c>
       <c r="N35">
-        <v>134.88244</v>
+        <v>134.37312</v>
       </c>
       <c r="O35">
-        <v>33.72061</v>
+        <v>33.59328</v>
       </c>
       <c r="P35">
-        <v>101.16183</v>
+        <v>100.77984</v>
       </c>
       <c r="Q35">
-        <v>106.97183</v>
+        <v>106.58984</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.117399035604942</v>
+        <v>0.1182858207870691</v>
       </c>
       <c r="T35">
-        <v>1.39559847115521</v>
+        <v>1.412883564927258</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>9.025105369250504</v>
+        <v>8.759661093684311</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09171114171946559</v>
+        <v>0.09152367958362008</v>
       </c>
       <c r="C36">
-        <v>598.1979249383173</v>
+        <v>590.8288224977489</v>
       </c>
       <c r="D36">
-        <v>733.9779249383173</v>
+        <v>736.128822497749</v>
       </c>
       <c r="E36">
-        <v>-331.1199999999999</v>
+        <v>-321.5999999999999</v>
       </c>
       <c r="F36">
-        <v>323.68</v>
+        <v>333.2</v>
       </c>
       <c r="G36">
         <v>187.9</v>
@@ -4233,28 +4233,28 @@
         <v>151.69</v>
       </c>
       <c r="M36">
-        <v>17.31688</v>
+        <v>17.8262</v>
       </c>
       <c r="N36">
-        <v>134.37312</v>
+        <v>133.8638</v>
       </c>
       <c r="O36">
-        <v>33.59328</v>
+        <v>33.46595</v>
       </c>
       <c r="P36">
-        <v>100.77984</v>
+        <v>100.39785</v>
       </c>
       <c r="Q36">
-        <v>106.58984</v>
+        <v>106.20785</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1182858207870691</v>
+        <v>0.1191998916671078</v>
       </c>
       <c r="T36">
-        <v>1.412883564927258</v>
+        <v>1.430700507738447</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.759661093684311</v>
+        <v>8.509385062436188</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09152367958362008</v>
+        <v>0.09133621744777452</v>
       </c>
       <c r="C37">
-        <v>590.8288224977489</v>
+        <v>583.4723633735333</v>
       </c>
       <c r="D37">
-        <v>736.128822497749</v>
+        <v>738.2923633735334</v>
       </c>
       <c r="E37">
-        <v>-321.5999999999999</v>
+        <v>-312.0799999999999</v>
       </c>
       <c r="F37">
-        <v>333.2</v>
+        <v>342.72</v>
       </c>
       <c r="G37">
         <v>187.9</v>
@@ -4315,28 +4315,28 @@
         <v>151.69</v>
       </c>
       <c r="M37">
-        <v>17.8262</v>
+        <v>18.33552</v>
       </c>
       <c r="N37">
-        <v>133.8638</v>
+        <v>133.35448</v>
       </c>
       <c r="O37">
-        <v>33.46595</v>
+        <v>33.33862</v>
       </c>
       <c r="P37">
-        <v>100.39785</v>
+        <v>100.01586</v>
       </c>
       <c r="Q37">
-        <v>106.20785</v>
+        <v>105.82586</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1191998916671078</v>
+        <v>0.1201425272621477</v>
       </c>
       <c r="T37">
-        <v>1.430700507738447</v>
+        <v>1.449074230012485</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>8.509385062436188</v>
+        <v>8.273013255146294</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09133621744777454</v>
+        <v>0.09114875531192901</v>
       </c>
       <c r="C38">
-        <v>583.4723633735332</v>
+        <v>576.128659373404</v>
       </c>
       <c r="D38">
-        <v>738.2923633735332</v>
+        <v>740.4686593734041</v>
       </c>
       <c r="E38">
-        <v>-312.08</v>
+        <v>-302.5599999999999</v>
       </c>
       <c r="F38">
-        <v>342.72</v>
+        <v>352.24</v>
       </c>
       <c r="G38">
         <v>187.9</v>
@@ -4397,28 +4397,28 @@
         <v>151.69</v>
       </c>
       <c r="M38">
-        <v>18.33552</v>
+        <v>18.84484</v>
       </c>
       <c r="N38">
-        <v>133.35448</v>
+        <v>132.84516</v>
       </c>
       <c r="O38">
-        <v>33.33862</v>
+        <v>33.21129</v>
       </c>
       <c r="P38">
-        <v>100.01586</v>
+        <v>99.63387</v>
       </c>
       <c r="Q38">
-        <v>105.82586</v>
+        <v>105.44387</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1201425272621477</v>
+        <v>0.1211150877967127</v>
       </c>
       <c r="T38">
-        <v>1.449074230012485</v>
+        <v>1.468031245057128</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.273013255146296</v>
+        <v>8.049418302304503</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09114875531192901</v>
+        <v>0.09096129317608347</v>
       </c>
       <c r="C39">
-        <v>576.128659373404</v>
+        <v>568.7978236273153</v>
       </c>
       <c r="D39">
-        <v>740.4686593734041</v>
+        <v>742.6578236273153</v>
       </c>
       <c r="E39">
-        <v>-302.5599999999999</v>
+        <v>-293.04</v>
       </c>
       <c r="F39">
-        <v>352.24</v>
+        <v>361.76</v>
       </c>
       <c r="G39">
         <v>187.9</v>
@@ -4479,28 +4479,28 @@
         <v>151.69</v>
       </c>
       <c r="M39">
-        <v>18.84484</v>
+        <v>19.35416</v>
       </c>
       <c r="N39">
-        <v>132.84516</v>
+        <v>132.33584</v>
       </c>
       <c r="O39">
-        <v>33.21129</v>
+        <v>33.08396</v>
       </c>
       <c r="P39">
-        <v>99.63387</v>
+        <v>99.25188</v>
       </c>
       <c r="Q39">
-        <v>105.44387</v>
+        <v>105.06188</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1211150877967127</v>
+        <v>0.1221190212517475</v>
       </c>
       <c r="T39">
-        <v>1.468031245057128</v>
+        <v>1.487599776716114</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>8.049418302304503</v>
+        <v>7.837591504875437</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09096129317608347</v>
+        <v>0.09077383104023794</v>
       </c>
       <c r="C40">
-        <v>568.7978236273153</v>
+        <v>561.479970607043</v>
       </c>
       <c r="D40">
-        <v>742.6578236273153</v>
+        <v>744.859970607043</v>
       </c>
       <c r="E40">
-        <v>-293.04</v>
+        <v>-283.5199999999999</v>
       </c>
       <c r="F40">
-        <v>361.76</v>
+        <v>371.28</v>
       </c>
       <c r="G40">
         <v>187.9</v>
@@ -4561,28 +4561,28 @@
         <v>151.69</v>
       </c>
       <c r="M40">
-        <v>19.35416</v>
+        <v>19.86348</v>
       </c>
       <c r="N40">
-        <v>132.33584</v>
+        <v>131.82652</v>
       </c>
       <c r="O40">
-        <v>33.08396</v>
+        <v>32.95663</v>
       </c>
       <c r="P40">
-        <v>99.25188</v>
+        <v>98.86989</v>
       </c>
       <c r="Q40">
-        <v>105.06188</v>
+        <v>104.67989</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1221190212517475</v>
+        <v>0.1231558705577671</v>
       </c>
       <c r="T40">
-        <v>1.487599776716114</v>
+        <v>1.507809899577034</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>7.837591504875437</v>
+        <v>7.63662762013504</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09077383104023794</v>
+        <v>0.09082636890439238</v>
       </c>
       <c r="C41">
-        <v>561.479970607043</v>
+        <v>551.3414840452836</v>
       </c>
       <c r="D41">
-        <v>744.859970607043</v>
+        <v>744.2414840452836</v>
       </c>
       <c r="E41">
-        <v>-283.5199999999999</v>
+        <v>-273.9999999999999</v>
       </c>
       <c r="F41">
-        <v>371.28</v>
+        <v>380.8</v>
       </c>
       <c r="G41">
         <v>187.9</v>
@@ -4643,45 +4643,45 @@
         <v>151.69</v>
       </c>
       <c r="M41">
-        <v>19.86348</v>
+        <v>20.67744</v>
       </c>
       <c r="N41">
-        <v>131.82652</v>
+        <v>131.01256</v>
       </c>
       <c r="O41">
-        <v>32.95663</v>
+        <v>32.75314</v>
       </c>
       <c r="P41">
-        <v>98.86989</v>
+        <v>98.25942000000001</v>
       </c>
       <c r="Q41">
-        <v>104.67989</v>
+        <v>104.06942</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1231558705577671</v>
+        <v>0.1242272815073207</v>
       </c>
       <c r="T41">
-        <v>1.507809899577034</v>
+        <v>1.528693693199984</v>
       </c>
       <c r="U41">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V41">
         <v>0.25</v>
       </c>
       <c r="W41">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y41">
-        <v>7.63662762013504</v>
+        <v>7.336014516303759</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09082636890439238</v>
+        <v>0.09064490676854686</v>
       </c>
       <c r="C42">
-        <v>551.3414840452836</v>
+        <v>543.9620589467772</v>
       </c>
       <c r="D42">
-        <v>744.2414840452836</v>
+        <v>746.3820589467773</v>
       </c>
       <c r="E42">
-        <v>-273.9999999999999</v>
+        <v>-264.4799999999999</v>
       </c>
       <c r="F42">
-        <v>380.8</v>
+        <v>390.3200000000001</v>
       </c>
       <c r="G42">
         <v>187.9</v>
@@ -4725,28 +4725,28 @@
         <v>151.69</v>
       </c>
       <c r="M42">
-        <v>20.67744</v>
+        <v>21.194376</v>
       </c>
       <c r="N42">
-        <v>131.01256</v>
+        <v>130.495624</v>
       </c>
       <c r="O42">
-        <v>32.75314</v>
+        <v>32.623906</v>
       </c>
       <c r="P42">
-        <v>98.25942000000001</v>
+        <v>97.87171799999999</v>
       </c>
       <c r="Q42">
-        <v>104.06942</v>
+        <v>103.681718</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1242272815073207</v>
+        <v>0.1253350114721133</v>
       </c>
       <c r="T42">
-        <v>1.528693693199984</v>
+        <v>1.550285412030493</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>7.336014516303759</v>
+        <v>7.157087332979276</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09064490676854686</v>
+        <v>0.09046344463270131</v>
       </c>
       <c r="C43">
-        <v>543.9620589467772</v>
+        <v>536.5949827373573</v>
       </c>
       <c r="D43">
-        <v>746.3820589467773</v>
+        <v>748.5349827373574</v>
       </c>
       <c r="E43">
-        <v>-264.4799999999999</v>
+        <v>-254.9599999999999</v>
       </c>
       <c r="F43">
-        <v>390.3200000000001</v>
+        <v>399.84</v>
       </c>
       <c r="G43">
         <v>187.9</v>
@@ -4807,28 +4807,28 @@
         <v>151.69</v>
       </c>
       <c r="M43">
-        <v>21.194376</v>
+        <v>21.711312</v>
       </c>
       <c r="N43">
-        <v>130.495624</v>
+        <v>129.978688</v>
       </c>
       <c r="O43">
-        <v>32.623906</v>
+        <v>32.494672</v>
       </c>
       <c r="P43">
-        <v>97.87171799999999</v>
+        <v>97.484016</v>
       </c>
       <c r="Q43">
-        <v>103.681718</v>
+        <v>103.294016</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1253350114721133</v>
+        <v>0.1264809390218988</v>
       </c>
       <c r="T43">
-        <v>1.550285412030493</v>
+        <v>1.572621672889639</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>7.157087332979276</v>
+        <v>6.986680491717865</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09046344463270133</v>
+        <v>0.09028198249685579</v>
       </c>
       <c r="C44">
-        <v>536.5949827373572</v>
+        <v>529.2403625865061</v>
       </c>
       <c r="D44">
-        <v>748.5349827373573</v>
+        <v>750.7003625865061</v>
       </c>
       <c r="E44">
-        <v>-254.96</v>
+        <v>-245.4399999999999</v>
       </c>
       <c r="F44">
-        <v>399.84</v>
+        <v>409.36</v>
       </c>
       <c r="G44">
         <v>187.9</v>
@@ -4889,28 +4889,28 @@
         <v>151.69</v>
       </c>
       <c r="M44">
-        <v>21.711312</v>
+        <v>22.228248</v>
       </c>
       <c r="N44">
-        <v>129.978688</v>
+        <v>129.461752</v>
       </c>
       <c r="O44">
-        <v>32.494672</v>
+        <v>32.365438</v>
       </c>
       <c r="P44">
-        <v>97.484016</v>
+        <v>97.09631399999999</v>
       </c>
       <c r="Q44">
-        <v>103.294016</v>
+        <v>102.906314</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1264809390218988</v>
+        <v>0.1276670745558874</v>
       </c>
       <c r="T44">
-        <v>1.572621672889639</v>
+        <v>1.595741662199983</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>6.986680491717866</v>
+        <v>6.824199550050007</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09028198249685579</v>
+        <v>0.09010052036101027</v>
       </c>
       <c r="C45">
-        <v>529.2403625865061</v>
+        <v>521.8983069073935</v>
       </c>
       <c r="D45">
-        <v>750.7003625865061</v>
+        <v>752.8783069073935</v>
       </c>
       <c r="E45">
-        <v>-245.4399999999999</v>
+        <v>-235.92</v>
       </c>
       <c r="F45">
-        <v>409.36</v>
+        <v>418.88</v>
       </c>
       <c r="G45">
         <v>187.9</v>
@@ -4971,28 +4971,28 @@
         <v>151.69</v>
       </c>
       <c r="M45">
-        <v>22.228248</v>
+        <v>22.745184</v>
       </c>
       <c r="N45">
-        <v>129.461752</v>
+        <v>128.944816</v>
       </c>
       <c r="O45">
-        <v>32.365438</v>
+        <v>32.236204</v>
       </c>
       <c r="P45">
-        <v>97.09631399999999</v>
+        <v>96.708612</v>
       </c>
       <c r="Q45">
-        <v>102.906314</v>
+        <v>102.518612</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1276670745558874</v>
+        <v>0.1288955720732326</v>
       </c>
       <c r="T45">
-        <v>1.595741662199983</v>
+        <v>1.619687365414269</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>6.824199550050007</v>
+        <v>6.66910410573069</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09010052036101027</v>
+        <v>0.08991905822516473</v>
       </c>
       <c r="C46">
-        <v>521.8983069073935</v>
+        <v>514.5689253749711</v>
       </c>
       <c r="D46">
-        <v>752.8783069073935</v>
+        <v>755.0689253749711</v>
       </c>
       <c r="E46">
-        <v>-235.92</v>
+        <v>-226.3999999999999</v>
       </c>
       <c r="F46">
-        <v>418.88</v>
+        <v>428.4</v>
       </c>
       <c r="G46">
         <v>187.9</v>
@@ -5053,28 +5053,28 @@
         <v>151.69</v>
       </c>
       <c r="M46">
-        <v>22.745184</v>
+        <v>23.26212</v>
       </c>
       <c r="N46">
-        <v>128.944816</v>
+        <v>128.42788</v>
       </c>
       <c r="O46">
-        <v>32.236204</v>
+        <v>32.10697</v>
       </c>
       <c r="P46">
-        <v>96.708612</v>
+        <v>96.32091</v>
       </c>
       <c r="Q46">
-        <v>102.518612</v>
+        <v>102.13091</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1288955720732326</v>
+        <v>0.1301687422275722</v>
       </c>
       <c r="T46">
-        <v>1.619687365414269</v>
+        <v>1.64450382147271</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.66910410573069</v>
+        <v>6.520901792270007</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08991905822516473</v>
+        <v>0.08973759608931919</v>
       </c>
       <c r="C47">
-        <v>514.5689253749711</v>
+        <v>507.2523289443808</v>
       </c>
       <c r="D47">
-        <v>755.0689253749711</v>
+        <v>757.2723289443809</v>
       </c>
       <c r="E47">
-        <v>-226.3999999999999</v>
+        <v>-216.8799999999999</v>
       </c>
       <c r="F47">
-        <v>428.4</v>
+        <v>437.92</v>
       </c>
       <c r="G47">
         <v>187.9</v>
@@ -5135,28 +5135,28 @@
         <v>151.69</v>
       </c>
       <c r="M47">
-        <v>23.26212</v>
+        <v>23.779056</v>
       </c>
       <c r="N47">
-        <v>128.42788</v>
+        <v>127.910944</v>
       </c>
       <c r="O47">
-        <v>32.10697</v>
+        <v>31.977736</v>
       </c>
       <c r="P47">
-        <v>96.32091</v>
+        <v>95.93320800000001</v>
       </c>
       <c r="Q47">
-        <v>102.13091</v>
+        <v>101.743208</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1301687422275722</v>
+        <v>0.1314890668320726</v>
       </c>
       <c r="T47">
-        <v>1.64450382147271</v>
+        <v>1.670239405533316</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>6.520901792270007</v>
+        <v>6.379143057655442</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08973759608931919</v>
+        <v>0.08955613395347366</v>
       </c>
       <c r="C48">
-        <v>507.2523289443808</v>
+        <v>499.9486298696903</v>
       </c>
       <c r="D48">
-        <v>757.2723289443809</v>
+        <v>759.4886298696904</v>
       </c>
       <c r="E48">
-        <v>-216.8799999999999</v>
+        <v>-207.3599999999999</v>
       </c>
       <c r="F48">
-        <v>437.92</v>
+        <v>447.4400000000001</v>
       </c>
       <c r="G48">
         <v>187.9</v>
@@ -5217,28 +5217,28 @@
         <v>151.69</v>
       </c>
       <c r="M48">
-        <v>23.779056</v>
+        <v>24.295992</v>
       </c>
       <c r="N48">
-        <v>127.910944</v>
+        <v>127.394008</v>
       </c>
       <c r="O48">
-        <v>31.977736</v>
+        <v>31.848502</v>
       </c>
       <c r="P48">
-        <v>95.93320800000001</v>
+        <v>95.545506</v>
       </c>
       <c r="Q48">
-        <v>101.743208</v>
+        <v>101.355506</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1314890668320726</v>
+        <v>0.1328592150065541</v>
       </c>
       <c r="T48">
-        <v>1.670239405533316</v>
+        <v>1.696946143709416</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.379143057655442</v>
+        <v>6.24341660962022</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08955613395347366</v>
+        <v>0.08937467181762812</v>
       </c>
       <c r="C49">
-        <v>499.9486298696903</v>
+        <v>492.6579417229557</v>
       </c>
       <c r="D49">
-        <v>759.4886298696904</v>
+        <v>761.7179417229557</v>
       </c>
       <c r="E49">
-        <v>-207.3599999999999</v>
+        <v>-197.8399999999999</v>
       </c>
       <c r="F49">
-        <v>447.4400000000001</v>
+        <v>456.96</v>
       </c>
       <c r="G49">
         <v>187.9</v>
@@ -5299,28 +5299,28 @@
         <v>151.69</v>
       </c>
       <c r="M49">
-        <v>24.295992</v>
+        <v>24.812928</v>
       </c>
       <c r="N49">
-        <v>127.394008</v>
+        <v>126.877072</v>
       </c>
       <c r="O49">
-        <v>31.848502</v>
+        <v>31.719268</v>
       </c>
       <c r="P49">
-        <v>95.545506</v>
+        <v>95.157804</v>
       </c>
       <c r="Q49">
-        <v>101.355506</v>
+        <v>100.967804</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1328592150065541</v>
+        <v>0.1342820611877464</v>
       </c>
       <c r="T49">
-        <v>1.696946143709416</v>
+        <v>1.724680064123059</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>6.24341660962022</v>
+        <v>6.113345430253132</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08937467181762812</v>
+        <v>0.08956070968178259</v>
       </c>
       <c r="C50">
-        <v>492.6579417229557</v>
+        <v>480.8525844560919</v>
       </c>
       <c r="D50">
-        <v>761.7179417229557</v>
+        <v>759.4325844560919</v>
       </c>
       <c r="E50">
-        <v>-197.84</v>
+        <v>-188.3199999999999</v>
       </c>
       <c r="F50">
-        <v>456.96</v>
+        <v>466.48</v>
       </c>
       <c r="G50">
         <v>187.9</v>
@@ -5381,45 +5381,45 @@
         <v>151.69</v>
       </c>
       <c r="M50">
-        <v>24.812928</v>
+        <v>25.796344</v>
       </c>
       <c r="N50">
-        <v>126.877072</v>
+        <v>125.893656</v>
       </c>
       <c r="O50">
-        <v>31.719268</v>
+        <v>31.473414</v>
       </c>
       <c r="P50">
-        <v>95.157804</v>
+        <v>94.420242</v>
       </c>
       <c r="Q50">
-        <v>100.967804</v>
+        <v>100.230242</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1342820611877464</v>
+        <v>0.1357607052583972</v>
       </c>
       <c r="T50">
-        <v>1.724680064123059</v>
+        <v>1.753501589258805</v>
       </c>
       <c r="U50">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V50">
         <v>0.25</v>
       </c>
       <c r="W50">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y50">
-        <v>6.113345430253132</v>
+        <v>5.880290633432396</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08956070968178259</v>
+        <v>0.08938674754593706</v>
       </c>
       <c r="C51">
-        <v>480.8525844560919</v>
+        <v>473.4691817040591</v>
       </c>
       <c r="D51">
-        <v>759.4325844560919</v>
+        <v>761.5691817040591</v>
       </c>
       <c r="E51">
-        <v>-188.3199999999999</v>
+        <v>-178.8</v>
       </c>
       <c r="F51">
-        <v>466.48</v>
+        <v>476</v>
       </c>
       <c r="G51">
         <v>187.9</v>
@@ -5463,28 +5463,28 @@
         <v>151.69</v>
       </c>
       <c r="M51">
-        <v>25.796344</v>
+        <v>26.3228</v>
       </c>
       <c r="N51">
-        <v>125.893656</v>
+        <v>125.3672</v>
       </c>
       <c r="O51">
-        <v>31.473414</v>
+        <v>31.3418</v>
       </c>
       <c r="P51">
-        <v>94.420242</v>
+        <v>94.02539999999999</v>
       </c>
       <c r="Q51">
-        <v>100.230242</v>
+        <v>99.83539999999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1357607052583972</v>
+        <v>0.1372984950918741</v>
       </c>
       <c r="T51">
-        <v>1.753501589258805</v>
+        <v>1.783475975399982</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.880290633432396</v>
+        <v>5.762684820763749</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08938674754593706</v>
+        <v>0.08921278541009152</v>
       </c>
       <c r="C52">
-        <v>473.4691817040591</v>
+        <v>466.0978351305278</v>
       </c>
       <c r="D52">
-        <v>761.5691817040591</v>
+        <v>763.7178351305278</v>
       </c>
       <c r="E52">
-        <v>-178.8</v>
+        <v>-169.28</v>
       </c>
       <c r="F52">
-        <v>476</v>
+        <v>485.52</v>
       </c>
       <c r="G52">
         <v>187.9</v>
@@ -5545,28 +5545,28 @@
         <v>151.69</v>
       </c>
       <c r="M52">
-        <v>26.3228</v>
+        <v>26.849256</v>
       </c>
       <c r="N52">
-        <v>125.3672</v>
+        <v>124.840744</v>
       </c>
       <c r="O52">
-        <v>31.3418</v>
+        <v>31.210186</v>
       </c>
       <c r="P52">
-        <v>94.02539999999999</v>
+        <v>93.63055800000001</v>
       </c>
       <c r="Q52">
-        <v>99.83539999999999</v>
+        <v>99.44055800000001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1372984950918741</v>
+        <v>0.1388990518573296</v>
       </c>
       <c r="T52">
-        <v>1.783475975399982</v>
+        <v>1.814673805873451</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.762684820763749</v>
+        <v>5.649691000748773</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08921278541009152</v>
+        <v>0.08903882327424599</v>
       </c>
       <c r="C53">
-        <v>466.0978351305278</v>
+        <v>458.738647068322</v>
       </c>
       <c r="D53">
-        <v>763.7178351305278</v>
+        <v>765.878647068322</v>
       </c>
       <c r="E53">
-        <v>-169.28</v>
+        <v>-159.7599999999999</v>
       </c>
       <c r="F53">
-        <v>485.52</v>
+        <v>495.04</v>
       </c>
       <c r="G53">
         <v>187.9</v>
@@ -5627,28 +5627,28 @@
         <v>151.69</v>
       </c>
       <c r="M53">
-        <v>26.849256</v>
+        <v>27.375712</v>
       </c>
       <c r="N53">
-        <v>124.840744</v>
+        <v>124.314288</v>
       </c>
       <c r="O53">
-        <v>31.210186</v>
+        <v>31.078572</v>
       </c>
       <c r="P53">
-        <v>93.63055800000001</v>
+        <v>93.235716</v>
       </c>
       <c r="Q53">
-        <v>99.44055800000001</v>
+        <v>99.045716</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1388990518573296</v>
+        <v>0.1405662984880125</v>
       </c>
       <c r="T53">
-        <v>1.814673805873451</v>
+        <v>1.847171545949981</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.649691000748773</v>
+        <v>5.541043096888218</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08903882327424599</v>
+        <v>0.08886486113840045</v>
       </c>
       <c r="C54">
-        <v>458.738647068322</v>
+        <v>451.3917210116875</v>
       </c>
       <c r="D54">
-        <v>765.878647068322</v>
+        <v>768.0517210116875</v>
       </c>
       <c r="E54">
-        <v>-159.7599999999999</v>
+        <v>-150.24</v>
       </c>
       <c r="F54">
-        <v>495.04</v>
+        <v>504.56</v>
       </c>
       <c r="G54">
         <v>187.9</v>
@@ -5709,28 +5709,28 @@
         <v>151.69</v>
       </c>
       <c r="M54">
-        <v>27.375712</v>
+        <v>27.902168</v>
       </c>
       <c r="N54">
-        <v>124.314288</v>
+        <v>123.787832</v>
       </c>
       <c r="O54">
-        <v>31.078572</v>
+        <v>30.946958</v>
       </c>
       <c r="P54">
-        <v>93.235716</v>
+        <v>92.840874</v>
       </c>
       <c r="Q54">
-        <v>99.045716</v>
+        <v>98.650874</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1405662984880125</v>
+        <v>0.1423044917838308</v>
       </c>
       <c r="T54">
-        <v>1.847171545949981</v>
+        <v>1.88105216858296</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.541043096888218</v>
+        <v>5.436495113928064</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08886486113840045</v>
+        <v>0.08869089900255492</v>
       </c>
       <c r="C55">
-        <v>451.3917210116875</v>
+        <v>444.0571616328131</v>
       </c>
       <c r="D55">
-        <v>768.0517210116875</v>
+        <v>770.2371616328131</v>
       </c>
       <c r="E55">
-        <v>-150.24</v>
+        <v>-140.7199999999999</v>
       </c>
       <c r="F55">
-        <v>504.56</v>
+        <v>514.08</v>
       </c>
       <c r="G55">
         <v>187.9</v>
@@ -5791,28 +5791,28 @@
         <v>151.69</v>
       </c>
       <c r="M55">
-        <v>27.902168</v>
+        <v>28.428624</v>
       </c>
       <c r="N55">
-        <v>123.787832</v>
+        <v>123.261376</v>
       </c>
       <c r="O55">
-        <v>30.946958</v>
+        <v>30.815344</v>
       </c>
       <c r="P55">
-        <v>92.840874</v>
+        <v>92.446032</v>
       </c>
       <c r="Q55">
-        <v>98.650874</v>
+        <v>98.256032</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1423044917838308</v>
+        <v>0.1441182587012063</v>
       </c>
       <c r="T55">
-        <v>1.88105216858296</v>
+        <v>1.916405861765198</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.436495113928064</v>
+        <v>5.335819278484952</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08869089900255492</v>
+        <v>0.08851693686670939</v>
       </c>
       <c r="C56">
-        <v>444.0571616328131</v>
+        <v>436.7350747986395</v>
       </c>
       <c r="D56">
-        <v>770.2371616328131</v>
+        <v>772.4350747986396</v>
       </c>
       <c r="E56">
-        <v>-140.7199999999999</v>
+        <v>-131.1999999999999</v>
       </c>
       <c r="F56">
-        <v>514.08</v>
+        <v>523.6</v>
       </c>
       <c r="G56">
         <v>187.9</v>
@@ -5873,28 +5873,28 @@
         <v>151.69</v>
       </c>
       <c r="M56">
-        <v>28.428624</v>
+        <v>28.95508</v>
       </c>
       <c r="N56">
-        <v>123.261376</v>
+        <v>122.73492</v>
       </c>
       <c r="O56">
-        <v>30.815344</v>
+        <v>30.68373</v>
       </c>
       <c r="P56">
-        <v>92.446032</v>
+        <v>92.05118999999999</v>
       </c>
       <c r="Q56">
-        <v>98.256032</v>
+        <v>97.86118999999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1441182587012063</v>
+        <v>0.1460126374815764</v>
       </c>
       <c r="T56">
-        <v>1.916405861765198</v>
+        <v>1.95333083019998</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.335819278484952</v>
+        <v>5.238804382512498</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08851693686670939</v>
+        <v>0.08834297473086383</v>
       </c>
       <c r="C57">
-        <v>436.7350747986395</v>
+        <v>429.4255675879534</v>
       </c>
       <c r="D57">
-        <v>772.4350747986396</v>
+        <v>774.6455675879535</v>
       </c>
       <c r="E57">
-        <v>-131.1999999999999</v>
+        <v>-121.6799999999999</v>
       </c>
       <c r="F57">
-        <v>523.6</v>
+        <v>533.12</v>
       </c>
       <c r="G57">
         <v>187.9</v>
@@ -5955,28 +5955,28 @@
         <v>151.69</v>
       </c>
       <c r="M57">
-        <v>28.95508</v>
+        <v>29.481536</v>
       </c>
       <c r="N57">
-        <v>122.73492</v>
+        <v>122.208464</v>
       </c>
       <c r="O57">
-        <v>30.68373</v>
+        <v>30.552116</v>
       </c>
       <c r="P57">
-        <v>92.05118999999999</v>
+        <v>91.65634799999999</v>
       </c>
       <c r="Q57">
-        <v>97.86118999999999</v>
+        <v>97.466348</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1460126374815764</v>
+        <v>0.1479931243883269</v>
       </c>
       <c r="T57">
-        <v>1.95333083019998</v>
+        <v>1.991934206290889</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.238804382512498</v>
+        <v>5.145254304253347</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08834297473086383</v>
+        <v>0.08816901259501832</v>
       </c>
       <c r="C58">
-        <v>429.4255675879534</v>
+        <v>422.1287483087757</v>
       </c>
       <c r="D58">
-        <v>774.6455675879535</v>
+        <v>776.8687483087758</v>
       </c>
       <c r="E58">
-        <v>-121.6799999999999</v>
+        <v>-112.1599999999999</v>
       </c>
       <c r="F58">
-        <v>533.12</v>
+        <v>542.6400000000001</v>
       </c>
       <c r="G58">
         <v>187.9</v>
@@ -6037,28 +6037,28 @@
         <v>151.69</v>
       </c>
       <c r="M58">
-        <v>29.481536</v>
+        <v>30.00799200000001</v>
       </c>
       <c r="N58">
-        <v>122.208464</v>
+        <v>121.682008</v>
       </c>
       <c r="O58">
-        <v>30.552116</v>
+        <v>30.420502</v>
       </c>
       <c r="P58">
-        <v>91.65634799999999</v>
+        <v>91.261506</v>
       </c>
       <c r="Q58">
-        <v>97.466348</v>
+        <v>97.071506</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1479931243883269</v>
+        <v>0.1500657269651589</v>
       </c>
       <c r="T58">
-        <v>1.991934206290889</v>
+        <v>2.032333088246491</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.145254304253347</v>
+        <v>5.054986684880481</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08816901259501832</v>
+        <v>0.08799505045917277</v>
       </c>
       <c r="C59">
-        <v>422.1287483087757</v>
+        <v>414.8447265160554</v>
       </c>
       <c r="D59">
-        <v>776.8687483087758</v>
+        <v>779.1047265160555</v>
       </c>
       <c r="E59">
-        <v>-112.1599999999999</v>
+        <v>-102.6399999999999</v>
       </c>
       <c r="F59">
-        <v>542.6400000000001</v>
+        <v>552.1600000000001</v>
       </c>
       <c r="G59">
         <v>187.9</v>
@@ -6119,28 +6119,28 @@
         <v>151.69</v>
       </c>
       <c r="M59">
-        <v>30.00799200000001</v>
+        <v>30.534448</v>
       </c>
       <c r="N59">
-        <v>121.682008</v>
+        <v>121.155552</v>
       </c>
       <c r="O59">
-        <v>30.420502</v>
+        <v>30.288888</v>
       </c>
       <c r="P59">
-        <v>91.261506</v>
+        <v>90.866664</v>
       </c>
       <c r="Q59">
-        <v>97.071506</v>
+        <v>96.676664</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1500657269651589</v>
+        <v>0.1522370249027923</v>
       </c>
       <c r="T59">
-        <v>2.032333088246491</v>
+        <v>2.074655726485693</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.054986684880481</v>
+        <v>4.967831742037713</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08799505045917277</v>
+        <v>0.08782108832332723</v>
       </c>
       <c r="C60">
-        <v>414.8447265160555</v>
+        <v>407.5736130296614</v>
       </c>
       <c r="D60">
-        <v>779.1047265160555</v>
+        <v>781.3536130296613</v>
       </c>
       <c r="E60">
-        <v>-102.64</v>
+        <v>-93.12</v>
       </c>
       <c r="F60">
-        <v>552.16</v>
+        <v>561.6799999999999</v>
       </c>
       <c r="G60">
         <v>187.9</v>
@@ -6201,28 +6201,28 @@
         <v>151.69</v>
       </c>
       <c r="M60">
-        <v>30.534448</v>
+        <v>31.060904</v>
       </c>
       <c r="N60">
-        <v>121.155552</v>
+        <v>120.629096</v>
       </c>
       <c r="O60">
-        <v>30.288888</v>
+        <v>30.157274</v>
       </c>
       <c r="P60">
-        <v>90.866664</v>
+        <v>90.471822</v>
       </c>
       <c r="Q60">
-        <v>96.676664</v>
+        <v>96.28182200000001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1522370249027923</v>
+        <v>0.1545142398129933</v>
       </c>
       <c r="T60">
-        <v>2.074655726485693</v>
+        <v>2.119042883663393</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.967831742037715</v>
+        <v>4.883631204037076</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08782108832332723</v>
+        <v>0.08764712618748172</v>
       </c>
       <c r="C61">
-        <v>407.5736130296614</v>
+        <v>400.3155199526935</v>
       </c>
       <c r="D61">
-        <v>781.3536130296613</v>
+        <v>783.6155199526935</v>
       </c>
       <c r="E61">
-        <v>-93.12</v>
+        <v>-83.60000000000002</v>
       </c>
       <c r="F61">
-        <v>561.6799999999999</v>
+        <v>571.1999999999999</v>
       </c>
       <c r="G61">
         <v>187.9</v>
@@ -6283,28 +6283,28 @@
         <v>151.69</v>
       </c>
       <c r="M61">
-        <v>31.060904</v>
+        <v>31.58736</v>
       </c>
       <c r="N61">
-        <v>120.629096</v>
+        <v>120.10264</v>
       </c>
       <c r="O61">
-        <v>30.157274</v>
+        <v>30.02566</v>
       </c>
       <c r="P61">
-        <v>90.471822</v>
+        <v>90.07698000000001</v>
       </c>
       <c r="Q61">
-        <v>96.28182200000001</v>
+        <v>95.88698000000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1545142398129933</v>
+        <v>0.1569053154687043</v>
       </c>
       <c r="T61">
-        <v>2.119042883663393</v>
+        <v>2.165649398699978</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.883631204037076</v>
+        <v>4.802237350636458</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08764712618748172</v>
+        <v>0.08747316405163617</v>
       </c>
       <c r="C62">
-        <v>400.3155199526935</v>
+        <v>393.0705606901108</v>
       </c>
       <c r="D62">
-        <v>783.6155199526935</v>
+        <v>785.8905606901109</v>
       </c>
       <c r="E62">
-        <v>-83.60000000000002</v>
+        <v>-74.07999999999993</v>
       </c>
       <c r="F62">
-        <v>571.1999999999999</v>
+        <v>580.72</v>
       </c>
       <c r="G62">
         <v>187.9</v>
@@ -6365,28 +6365,28 @@
         <v>151.69</v>
       </c>
       <c r="M62">
-        <v>31.58736</v>
+        <v>32.113816</v>
       </c>
       <c r="N62">
-        <v>120.10264</v>
+        <v>119.576184</v>
       </c>
       <c r="O62">
-        <v>30.02566</v>
+        <v>29.894046</v>
       </c>
       <c r="P62">
-        <v>90.07698000000001</v>
+        <v>89.68213799999999</v>
       </c>
       <c r="Q62">
-        <v>95.88698000000001</v>
+        <v>95.492138</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1569053154687043</v>
+        <v>0.1594190103888107</v>
       </c>
       <c r="T62">
-        <v>2.165649398699978</v>
+        <v>2.214645991430747</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.802237350636458</v>
+        <v>4.723512148167007</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08747316405163617</v>
+        <v>0.08729920191579064</v>
       </c>
       <c r="C63">
-        <v>393.0705606901108</v>
+        <v>385.8388499676834</v>
       </c>
       <c r="D63">
-        <v>785.8905606901109</v>
+        <v>788.1788499676834</v>
       </c>
       <c r="E63">
-        <v>-74.07999999999993</v>
+        <v>-64.55999999999995</v>
       </c>
       <c r="F63">
-        <v>580.72</v>
+        <v>590.24</v>
       </c>
       <c r="G63">
         <v>187.9</v>
@@ -6447,28 +6447,28 @@
         <v>151.69</v>
       </c>
       <c r="M63">
-        <v>32.113816</v>
+        <v>32.640272</v>
       </c>
       <c r="N63">
-        <v>119.576184</v>
+        <v>119.049728</v>
       </c>
       <c r="O63">
-        <v>29.894046</v>
+        <v>29.762432</v>
       </c>
       <c r="P63">
-        <v>89.68213799999999</v>
+        <v>89.287296</v>
       </c>
       <c r="Q63">
-        <v>95.492138</v>
+        <v>95.097296</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1594190103888107</v>
+        <v>0.1620650050415543</v>
       </c>
       <c r="T63">
-        <v>2.214645991430747</v>
+        <v>2.266221352199977</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.723512148167007</v>
+        <v>4.647326468357861</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08729920191579064</v>
+        <v>0.0871252397799451</v>
       </c>
       <c r="C64">
-        <v>385.8388499676834</v>
+        <v>378.6205038512785</v>
       </c>
       <c r="D64">
-        <v>788.1788499676834</v>
+        <v>790.4805038512785</v>
       </c>
       <c r="E64">
-        <v>-64.55999999999995</v>
+        <v>-55.03999999999996</v>
       </c>
       <c r="F64">
-        <v>590.24</v>
+        <v>599.76</v>
       </c>
       <c r="G64">
         <v>187.9</v>
@@ -6529,28 +6529,28 @@
         <v>151.69</v>
       </c>
       <c r="M64">
-        <v>32.640272</v>
+        <v>33.166728</v>
       </c>
       <c r="N64">
-        <v>119.049728</v>
+        <v>118.523272</v>
       </c>
       <c r="O64">
-        <v>29.762432</v>
+        <v>29.630818</v>
       </c>
       <c r="P64">
-        <v>89.287296</v>
+        <v>88.89245399999999</v>
       </c>
       <c r="Q64">
-        <v>95.097296</v>
+        <v>94.70245399999999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1620650050415543</v>
+        <v>0.1648540264322841</v>
       </c>
       <c r="T64">
-        <v>2.266221352199977</v>
+        <v>2.320584570308085</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.647326468357861</v>
+        <v>4.57355938155853</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.0871252397799451</v>
+        <v>0.08695127764409957</v>
       </c>
       <c r="C65">
-        <v>378.6205038512785</v>
+        <v>371.4156397664842</v>
       </c>
       <c r="D65">
-        <v>790.4805038512785</v>
+        <v>792.7956397664842</v>
       </c>
       <c r="E65">
-        <v>-55.03999999999996</v>
+        <v>-45.51999999999998</v>
       </c>
       <c r="F65">
-        <v>599.76</v>
+        <v>609.28</v>
       </c>
       <c r="G65">
         <v>187.9</v>
@@ -6611,28 +6611,28 @@
         <v>151.69</v>
       </c>
       <c r="M65">
-        <v>33.166728</v>
+        <v>33.693184</v>
       </c>
       <c r="N65">
-        <v>118.523272</v>
+        <v>117.996816</v>
       </c>
       <c r="O65">
-        <v>29.630818</v>
+        <v>29.499204</v>
       </c>
       <c r="P65">
-        <v>88.89245399999999</v>
+        <v>88.497612</v>
       </c>
       <c r="Q65">
-        <v>94.70245399999999</v>
+        <v>94.30761200000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1648540264322841</v>
+        <v>0.1677979934558322</v>
       </c>
       <c r="T65">
-        <v>2.320584570308085</v>
+        <v>2.377967967199976</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.57355938155853</v>
+        <v>4.502097516221678</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08695127764409957</v>
+        <v>0.08799606550825403</v>
       </c>
       <c r="C66">
-        <v>371.4156397664842</v>
+        <v>348.1916425089219</v>
       </c>
       <c r="D66">
-        <v>792.7956397664842</v>
+        <v>779.091642508922</v>
       </c>
       <c r="E66">
-        <v>-45.51999999999998</v>
+        <v>-35.99999999999989</v>
       </c>
       <c r="F66">
-        <v>609.28</v>
+        <v>618.8000000000001</v>
       </c>
       <c r="G66">
         <v>187.9</v>
@@ -6693,45 +6693,45 @@
         <v>151.69</v>
       </c>
       <c r="M66">
-        <v>33.693184</v>
+        <v>35.76664000000001</v>
       </c>
       <c r="N66">
-        <v>117.996816</v>
+        <v>115.92336</v>
       </c>
       <c r="O66">
-        <v>29.499204</v>
+        <v>28.98084</v>
       </c>
       <c r="P66">
-        <v>88.497612</v>
+        <v>86.94251999999999</v>
       </c>
       <c r="Q66">
-        <v>94.30761200000001</v>
+        <v>92.75251999999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1677979934558322</v>
+        <v>0.1709101871664401</v>
       </c>
       <c r="T66">
-        <v>2.377967967199976</v>
+        <v>2.438630415342832</v>
       </c>
       <c r="U66">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V66">
         <v>0.25</v>
       </c>
       <c r="W66">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y66">
-        <v>4.502097516221678</v>
+        <v>4.241102882462539</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08799606550825403</v>
+        <v>0.0878408533724085</v>
       </c>
       <c r="C67">
-        <v>348.1916425089219</v>
+        <v>340.6774478560903</v>
       </c>
       <c r="D67">
-        <v>779.091642508922</v>
+        <v>781.0974478560904</v>
       </c>
       <c r="E67">
-        <v>-35.99999999999989</v>
+        <v>-26.4799999999999</v>
       </c>
       <c r="F67">
-        <v>618.8000000000001</v>
+        <v>628.3200000000001</v>
       </c>
       <c r="G67">
         <v>187.9</v>
@@ -6775,28 +6775,28 @@
         <v>151.69</v>
       </c>
       <c r="M67">
-        <v>35.76664000000001</v>
+        <v>36.31689600000001</v>
       </c>
       <c r="N67">
-        <v>115.92336</v>
+        <v>115.373104</v>
       </c>
       <c r="O67">
-        <v>28.98084</v>
+        <v>28.843276</v>
       </c>
       <c r="P67">
-        <v>86.94251999999999</v>
+        <v>86.52982799999998</v>
       </c>
       <c r="Q67">
-        <v>92.75251999999999</v>
+        <v>92.33982799999998</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1709101871664401</v>
+        <v>0.1742054510953192</v>
       </c>
       <c r="T67">
-        <v>2.438630415342832</v>
+        <v>2.50286124278821</v>
       </c>
       <c r="U67">
         <v>0.0578</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.241102882462539</v>
+        <v>4.176843747879774</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.0878408533724085</v>
+        <v>0.08768564123656297</v>
       </c>
       <c r="C68">
-        <v>340.6774478560903</v>
+        <v>333.1736079283057</v>
       </c>
       <c r="D68">
-        <v>781.0974478560904</v>
+        <v>783.1136079283058</v>
       </c>
       <c r="E68">
-        <v>-26.4799999999999</v>
+        <v>-16.95999999999992</v>
       </c>
       <c r="F68">
-        <v>628.3200000000001</v>
+        <v>637.84</v>
       </c>
       <c r="G68">
         <v>187.9</v>
@@ -6857,28 +6857,28 @@
         <v>151.69</v>
       </c>
       <c r="M68">
-        <v>36.31689600000001</v>
+        <v>36.867152</v>
       </c>
       <c r="N68">
-        <v>115.373104</v>
+        <v>114.822848</v>
       </c>
       <c r="O68">
-        <v>28.843276</v>
+        <v>28.705712</v>
       </c>
       <c r="P68">
-        <v>86.52982799999998</v>
+        <v>86.11713599999999</v>
       </c>
       <c r="Q68">
-        <v>92.33982799999998</v>
+        <v>91.92713599999999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1742054510953192</v>
+        <v>0.1777004279895848</v>
       </c>
       <c r="T68">
-        <v>2.50286124278821</v>
+        <v>2.570984847654519</v>
       </c>
       <c r="U68">
         <v>0.0578</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.176843747879774</v>
+        <v>4.114502796418882</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08768564123656297</v>
+        <v>0.08753042910071743</v>
       </c>
       <c r="C69">
-        <v>333.1736079283057</v>
+        <v>325.680203115574</v>
       </c>
       <c r="D69">
-        <v>783.1136079283058</v>
+        <v>785.1402031155741</v>
       </c>
       <c r="E69">
-        <v>-16.95999999999992</v>
+        <v>-7.439999999999941</v>
       </c>
       <c r="F69">
-        <v>637.84</v>
+        <v>647.36</v>
       </c>
       <c r="G69">
         <v>187.9</v>
@@ -6939,28 +6939,28 @@
         <v>151.69</v>
       </c>
       <c r="M69">
-        <v>36.867152</v>
+        <v>37.417408</v>
       </c>
       <c r="N69">
-        <v>114.822848</v>
+        <v>114.272592</v>
       </c>
       <c r="O69">
-        <v>28.705712</v>
+        <v>28.568148</v>
       </c>
       <c r="P69">
-        <v>86.11713599999999</v>
+        <v>85.704444</v>
       </c>
       <c r="Q69">
-        <v>91.92713599999999</v>
+        <v>91.514444</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1777004279895848</v>
+        <v>0.181413840939742</v>
       </c>
       <c r="T69">
-        <v>2.570984847654519</v>
+        <v>2.643366177824973</v>
       </c>
       <c r="U69">
         <v>0.0578</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.114502796418882</v>
+        <v>4.053995402353899</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08753042910071743</v>
+        <v>0.0891864669648719</v>
       </c>
       <c r="C70">
-        <v>325.680203115574</v>
+        <v>295.0639576981475</v>
       </c>
       <c r="D70">
-        <v>785.1402031155741</v>
+        <v>764.0439576981477</v>
       </c>
       <c r="E70">
-        <v>-7.439999999999941</v>
+        <v>2.080000000000155</v>
       </c>
       <c r="F70">
-        <v>647.36</v>
+        <v>656.8800000000001</v>
       </c>
       <c r="G70">
         <v>187.9</v>
@@ -7021,45 +7021,45 @@
         <v>151.69</v>
       </c>
       <c r="M70">
-        <v>37.417408</v>
+        <v>40.26674400000001</v>
       </c>
       <c r="N70">
-        <v>114.272592</v>
+        <v>111.423256</v>
       </c>
       <c r="O70">
-        <v>28.568148</v>
+        <v>27.855814</v>
       </c>
       <c r="P70">
-        <v>85.704444</v>
+        <v>83.56744199999999</v>
       </c>
       <c r="Q70">
-        <v>91.514444</v>
+        <v>89.37744199999999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.181413840939742</v>
+        <v>0.1853668289189417</v>
       </c>
       <c r="T70">
-        <v>2.643366177824973</v>
+        <v>2.720417271232231</v>
       </c>
       <c r="U70">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V70">
         <v>0.25</v>
       </c>
       <c r="W70">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y70">
-        <v>4.053995402353899</v>
+        <v>3.767128526706802</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.0891864669648719</v>
+        <v>0.08905750482902636</v>
       </c>
       <c r="C71">
-        <v>295.0639576981475</v>
+        <v>287.146014588324</v>
       </c>
       <c r="D71">
-        <v>764.0439576981477</v>
+        <v>765.6460145883241</v>
       </c>
       <c r="E71">
-        <v>2.080000000000155</v>
+        <v>11.60000000000014</v>
       </c>
       <c r="F71">
-        <v>656.8800000000001</v>
+        <v>666.4000000000001</v>
       </c>
       <c r="G71">
         <v>187.9</v>
@@ -7103,28 +7103,28 @@
         <v>151.69</v>
       </c>
       <c r="M71">
-        <v>40.26674400000001</v>
+        <v>40.85032</v>
       </c>
       <c r="N71">
-        <v>111.423256</v>
+        <v>110.83968</v>
       </c>
       <c r="O71">
-        <v>27.855814</v>
+        <v>27.70992</v>
       </c>
       <c r="P71">
-        <v>83.56744199999999</v>
+        <v>83.12975999999999</v>
       </c>
       <c r="Q71">
-        <v>89.37744199999999</v>
+        <v>88.93975999999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1853668289189417</v>
+        <v>0.1895833494300879</v>
       </c>
       <c r="T71">
-        <v>2.720417271232231</v>
+        <v>2.802605104199972</v>
       </c>
       <c r="U71">
         <v>0.0613</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.767128526706802</v>
+        <v>3.713312404896705</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08905750482902636</v>
+        <v>0.08892854269318085</v>
       </c>
       <c r="C72">
-        <v>287.146014588324</v>
+        <v>279.2348040210759</v>
       </c>
       <c r="D72">
-        <v>765.6460145883241</v>
+        <v>767.254804021076</v>
       </c>
       <c r="E72">
-        <v>11.60000000000014</v>
+        <v>21.12000000000012</v>
       </c>
       <c r="F72">
-        <v>666.4000000000001</v>
+        <v>675.9200000000001</v>
       </c>
       <c r="G72">
         <v>187.9</v>
@@ -7185,28 +7185,28 @@
         <v>151.69</v>
       </c>
       <c r="M72">
-        <v>40.85032</v>
+        <v>41.433896</v>
       </c>
       <c r="N72">
-        <v>110.83968</v>
+        <v>110.256104</v>
       </c>
       <c r="O72">
-        <v>27.70992</v>
+        <v>27.564026</v>
       </c>
       <c r="P72">
-        <v>83.12975999999999</v>
+        <v>82.692078</v>
       </c>
       <c r="Q72">
-        <v>88.93975999999999</v>
+        <v>88.502078</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1895833494300879</v>
+        <v>0.1940906644592443</v>
       </c>
       <c r="T72">
-        <v>2.802605104199972</v>
+        <v>2.890461063579282</v>
       </c>
       <c r="U72">
         <v>0.0613</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.713312404896705</v>
+        <v>3.66101223017985</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08892854269318085</v>
+        <v>0.08879958055733531</v>
       </c>
       <c r="C73">
-        <v>279.234804021076</v>
+        <v>271.3303685253921</v>
       </c>
       <c r="D73">
-        <v>767.254804021076</v>
+        <v>768.8703685253921</v>
       </c>
       <c r="E73">
-        <v>21.12</v>
+        <v>30.63999999999999</v>
       </c>
       <c r="F73">
-        <v>675.92</v>
+        <v>685.4399999999999</v>
       </c>
       <c r="G73">
         <v>187.9</v>
@@ -7267,28 +7267,28 @@
         <v>151.69</v>
       </c>
       <c r="M73">
-        <v>41.433896</v>
+        <v>42.017472</v>
       </c>
       <c r="N73">
-        <v>110.256104</v>
+        <v>109.672528</v>
       </c>
       <c r="O73">
-        <v>27.564026</v>
+        <v>27.418132</v>
       </c>
       <c r="P73">
-        <v>82.692078</v>
+        <v>82.254396</v>
       </c>
       <c r="Q73">
-        <v>88.502078</v>
+        <v>88.064396</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1940906644592442</v>
+        <v>0.1989199305619118</v>
       </c>
       <c r="T73">
-        <v>2.890461063579281</v>
+        <v>2.984592448628541</v>
       </c>
       <c r="U73">
         <v>0.0613</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.661012230179851</v>
+        <v>3.61016483809402</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08879958055733531</v>
+        <v>0.08867061842148977</v>
       </c>
       <c r="C74">
-        <v>271.3303685253921</v>
+        <v>263.4327509892192</v>
       </c>
       <c r="D74">
-        <v>768.8703685253921</v>
+        <v>770.4927509892193</v>
       </c>
       <c r="E74">
-        <v>30.63999999999999</v>
+        <v>40.16000000000008</v>
       </c>
       <c r="F74">
-        <v>685.4399999999999</v>
+        <v>694.96</v>
       </c>
       <c r="G74">
         <v>187.9</v>
@@ -7349,28 +7349,28 @@
         <v>151.69</v>
       </c>
       <c r="M74">
-        <v>42.017472</v>
+        <v>42.60104800000001</v>
       </c>
       <c r="N74">
-        <v>109.672528</v>
+        <v>109.088952</v>
       </c>
       <c r="O74">
-        <v>27.418132</v>
+        <v>27.272238</v>
       </c>
       <c r="P74">
-        <v>82.254396</v>
+        <v>81.81671399999999</v>
       </c>
       <c r="Q74">
-        <v>88.064396</v>
+        <v>87.62671399999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1989199305619118</v>
+        <v>0.2041069200795917</v>
       </c>
       <c r="T74">
-        <v>2.984592448628541</v>
+        <v>3.085696528866635</v>
       </c>
       <c r="U74">
         <v>0.0613</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.61016483809402</v>
+        <v>3.560710525243416</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08867061842148977</v>
+        <v>0.08854165628564423</v>
       </c>
       <c r="C75">
-        <v>263.4327509892192</v>
+        <v>255.5419946632595</v>
       </c>
       <c r="D75">
-        <v>770.4927509892193</v>
+        <v>772.1219946632596</v>
       </c>
       <c r="E75">
-        <v>40.16000000000008</v>
+        <v>49.68000000000006</v>
       </c>
       <c r="F75">
-        <v>694.96</v>
+        <v>704.48</v>
       </c>
       <c r="G75">
         <v>187.9</v>
@@ -7431,28 +7431,28 @@
         <v>151.69</v>
       </c>
       <c r="M75">
-        <v>42.60104800000001</v>
+        <v>43.184624</v>
       </c>
       <c r="N75">
-        <v>109.088952</v>
+        <v>108.505376</v>
       </c>
       <c r="O75">
-        <v>27.272238</v>
+        <v>27.126344</v>
       </c>
       <c r="P75">
-        <v>81.81671399999999</v>
+        <v>81.379032</v>
       </c>
       <c r="Q75">
-        <v>87.62671399999999</v>
+        <v>87.189032</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2041069200795917</v>
+        <v>0.2096929087909393</v>
       </c>
       <c r="T75">
-        <v>3.085696528866635</v>
+        <v>3.19457784604612</v>
       </c>
       <c r="U75">
         <v>0.0613</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.560710525243416</v>
+        <v>3.51259281544283</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08854165628564423</v>
+        <v>0.08998769414979871</v>
       </c>
       <c r="C76">
-        <v>255.5419946632595</v>
+        <v>228.1388522917964</v>
       </c>
       <c r="D76">
-        <v>772.1219946632596</v>
+        <v>754.2388522917964</v>
       </c>
       <c r="E76">
-        <v>49.68000000000006</v>
+        <v>59.20000000000005</v>
       </c>
       <c r="F76">
-        <v>704.48</v>
+        <v>714</v>
       </c>
       <c r="G76">
         <v>187.9</v>
@@ -7513,45 +7513,45 @@
         <v>151.69</v>
       </c>
       <c r="M76">
-        <v>43.184624</v>
+        <v>45.7674</v>
       </c>
       <c r="N76">
-        <v>108.505376</v>
+        <v>105.9226</v>
       </c>
       <c r="O76">
-        <v>27.126344</v>
+        <v>26.48065</v>
       </c>
       <c r="P76">
-        <v>81.379032</v>
+        <v>79.44194999999999</v>
       </c>
       <c r="Q76">
-        <v>87.189032</v>
+        <v>85.25194999999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2096929087909393</v>
+        <v>0.2157257765991948</v>
       </c>
       <c r="T76">
-        <v>3.19457784604612</v>
+        <v>3.312169668599966</v>
       </c>
       <c r="U76">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V76">
         <v>0.25</v>
       </c>
       <c r="W76">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y76">
-        <v>3.51259281544283</v>
+        <v>3.3143678688324</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08998769414979871</v>
+        <v>0.08987973201395316</v>
       </c>
       <c r="C77">
-        <v>228.1388522917964</v>
+        <v>219.9253548146738</v>
       </c>
       <c r="D77">
-        <v>754.2388522917964</v>
+        <v>755.5453548146738</v>
       </c>
       <c r="E77">
-        <v>59.20000000000005</v>
+        <v>68.72000000000003</v>
       </c>
       <c r="F77">
-        <v>714</v>
+        <v>723.52</v>
       </c>
       <c r="G77">
         <v>187.9</v>
@@ -7595,28 +7595,28 @@
         <v>151.69</v>
       </c>
       <c r="M77">
-        <v>45.7674</v>
+        <v>46.377632</v>
       </c>
       <c r="N77">
-        <v>105.9226</v>
+        <v>105.312368</v>
       </c>
       <c r="O77">
-        <v>26.48065</v>
+        <v>26.328092</v>
       </c>
       <c r="P77">
-        <v>79.44194999999999</v>
+        <v>78.98427599999999</v>
       </c>
       <c r="Q77">
-        <v>85.25194999999999</v>
+        <v>84.794276</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2157257765991948</v>
+        <v>0.2222613833914715</v>
       </c>
       <c r="T77">
-        <v>3.312169668599966</v>
+        <v>3.439560809699965</v>
       </c>
       <c r="U77">
         <v>0.0641</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.3143678688324</v>
+        <v>3.270757765295132</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08987973201395316</v>
+        <v>0.08977176987810763</v>
       </c>
       <c r="C78">
-        <v>219.9253548146738</v>
+        <v>211.7163914735669</v>
       </c>
       <c r="D78">
-        <v>755.5453548146738</v>
+        <v>756.8563914735669</v>
       </c>
       <c r="E78">
-        <v>68.72000000000003</v>
+        <v>78.24000000000001</v>
       </c>
       <c r="F78">
-        <v>723.52</v>
+        <v>733.04</v>
       </c>
       <c r="G78">
         <v>187.9</v>
@@ -7677,28 +7677,28 @@
         <v>151.69</v>
       </c>
       <c r="M78">
-        <v>46.377632</v>
+        <v>46.987864</v>
       </c>
       <c r="N78">
-        <v>105.312368</v>
+        <v>104.702136</v>
       </c>
       <c r="O78">
-        <v>26.328092</v>
+        <v>26.175534</v>
       </c>
       <c r="P78">
-        <v>78.98427599999999</v>
+        <v>78.526602</v>
       </c>
       <c r="Q78">
-        <v>84.794276</v>
+        <v>84.336602</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2222613833914715</v>
+        <v>0.2293653038178592</v>
       </c>
       <c r="T78">
-        <v>3.439560809699965</v>
+        <v>3.578029441330398</v>
       </c>
       <c r="U78">
         <v>0.0641</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.270757765295132</v>
+        <v>3.22828039171987</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08977176987810763</v>
+        <v>0.08966380774226208</v>
       </c>
       <c r="C79">
-        <v>211.7163914735669</v>
+        <v>203.5119859126606</v>
       </c>
       <c r="D79">
-        <v>756.8563914735669</v>
+        <v>758.1719859126607</v>
       </c>
       <c r="E79">
-        <v>78.24000000000001</v>
+        <v>87.7600000000001</v>
       </c>
       <c r="F79">
-        <v>733.04</v>
+        <v>742.5600000000001</v>
       </c>
       <c r="G79">
         <v>187.9</v>
@@ -7759,28 +7759,28 @@
         <v>151.69</v>
       </c>
       <c r="M79">
-        <v>46.987864</v>
+        <v>47.59809600000001</v>
       </c>
       <c r="N79">
-        <v>104.702136</v>
+        <v>104.091904</v>
       </c>
       <c r="O79">
-        <v>26.175534</v>
+        <v>26.022976</v>
       </c>
       <c r="P79">
-        <v>78.526602</v>
+        <v>78.068928</v>
       </c>
       <c r="Q79">
-        <v>84.336602</v>
+        <v>83.878928</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2293653038178592</v>
+        <v>0.2371150351921004</v>
       </c>
       <c r="T79">
-        <v>3.578029441330398</v>
+        <v>3.72908613038178</v>
       </c>
       <c r="U79">
         <v>0.0641</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.22828039171987</v>
+        <v>3.186892181569616</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08966380774226208</v>
+        <v>0.08955584560641655</v>
       </c>
       <c r="C80">
-        <v>203.5119859126606</v>
+        <v>195.3121619408226</v>
       </c>
       <c r="D80">
-        <v>758.1719859126607</v>
+        <v>759.4921619408227</v>
       </c>
       <c r="E80">
-        <v>87.7600000000001</v>
+        <v>97.28000000000009</v>
       </c>
       <c r="F80">
-        <v>742.5600000000001</v>
+        <v>752.08</v>
       </c>
       <c r="G80">
         <v>187.9</v>
@@ -7841,28 +7841,28 @@
         <v>151.69</v>
       </c>
       <c r="M80">
-        <v>47.59809600000001</v>
+        <v>48.20832800000001</v>
       </c>
       <c r="N80">
-        <v>104.091904</v>
+        <v>103.481672</v>
       </c>
       <c r="O80">
-        <v>26.022976</v>
+        <v>25.870418</v>
       </c>
       <c r="P80">
-        <v>78.068928</v>
+        <v>77.61125399999999</v>
       </c>
       <c r="Q80">
-        <v>83.878928</v>
+        <v>83.42125399999999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2371150351921004</v>
+        <v>0.2456028362210312</v>
       </c>
       <c r="T80">
-        <v>3.72908613038178</v>
+        <v>3.894529170771389</v>
       </c>
       <c r="U80">
         <v>0.0641</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.186892181569616</v>
+        <v>3.146551774207974</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08955584560641655</v>
+        <v>0.08944788347057103</v>
       </c>
       <c r="C81">
-        <v>195.3121619408226</v>
+        <v>187.1169435330395</v>
       </c>
       <c r="D81">
-        <v>759.4921619408227</v>
+        <v>760.8169435330395</v>
       </c>
       <c r="E81">
-        <v>97.28000000000009</v>
+        <v>106.8000000000001</v>
       </c>
       <c r="F81">
-        <v>752.08</v>
+        <v>761.6</v>
       </c>
       <c r="G81">
         <v>187.9</v>
@@ -7923,28 +7923,28 @@
         <v>151.69</v>
       </c>
       <c r="M81">
-        <v>48.20832800000001</v>
+        <v>48.81856000000001</v>
       </c>
       <c r="N81">
-        <v>103.481672</v>
+        <v>102.87144</v>
       </c>
       <c r="O81">
-        <v>25.870418</v>
+        <v>25.71786</v>
       </c>
       <c r="P81">
-        <v>77.61125399999999</v>
+        <v>77.15357999999999</v>
       </c>
       <c r="Q81">
-        <v>83.42125399999999</v>
+        <v>82.96357999999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2456028362210312</v>
+        <v>0.2549394173528551</v>
       </c>
       <c r="T81">
-        <v>3.894529170771389</v>
+        <v>4.076516515199959</v>
       </c>
       <c r="U81">
         <v>0.0641</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.146551774207974</v>
+        <v>3.107219877030375</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08944788347057103</v>
+        <v>0.08933992133472549</v>
       </c>
       <c r="C82">
-        <v>187.1169435330395</v>
+        <v>178.9263548318693</v>
       </c>
       <c r="D82">
-        <v>760.8169435330395</v>
+        <v>762.1463548318693</v>
       </c>
       <c r="E82">
-        <v>106.8000000000001</v>
+        <v>116.3200000000001</v>
       </c>
       <c r="F82">
-        <v>761.6</v>
+        <v>771.12</v>
       </c>
       <c r="G82">
         <v>187.9</v>
@@ -8005,28 +8005,28 @@
         <v>151.69</v>
       </c>
       <c r="M82">
-        <v>48.81856000000001</v>
+        <v>49.428792</v>
       </c>
       <c r="N82">
-        <v>102.87144</v>
+        <v>102.261208</v>
       </c>
       <c r="O82">
-        <v>25.71786</v>
+        <v>25.565302</v>
       </c>
       <c r="P82">
-        <v>77.15357999999999</v>
+        <v>76.69590599999999</v>
       </c>
       <c r="Q82">
-        <v>82.96357999999999</v>
+        <v>82.505906</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2549394173528551</v>
+        <v>0.2652587964985552</v>
       </c>
       <c r="T82">
-        <v>4.076516515199959</v>
+        <v>4.277660422199957</v>
       </c>
       <c r="U82">
         <v>0.0641</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.107219877030375</v>
+        <v>3.068859137807778</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08933992133472549</v>
+        <v>0.08923195919887994</v>
       </c>
       <c r="C83">
-        <v>178.9263548318693</v>
+        <v>170.7404201489057</v>
       </c>
       <c r="D83">
-        <v>762.1463548318693</v>
+        <v>763.4804201489059</v>
       </c>
       <c r="E83">
-        <v>116.3200000000001</v>
+        <v>125.8400000000001</v>
       </c>
       <c r="F83">
-        <v>771.12</v>
+        <v>780.6400000000001</v>
       </c>
       <c r="G83">
         <v>187.9</v>
@@ -8087,28 +8087,28 @@
         <v>151.69</v>
       </c>
       <c r="M83">
-        <v>49.428792</v>
+        <v>50.03902400000001</v>
       </c>
       <c r="N83">
-        <v>102.261208</v>
+        <v>101.650976</v>
       </c>
       <c r="O83">
-        <v>25.565302</v>
+        <v>25.412744</v>
       </c>
       <c r="P83">
-        <v>76.69590599999999</v>
+        <v>76.23823199999998</v>
       </c>
       <c r="Q83">
-        <v>82.505906</v>
+        <v>82.04823199999998</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2652587964985552</v>
+        <v>0.2767247733271109</v>
       </c>
       <c r="T83">
-        <v>4.277660422199957</v>
+        <v>4.501153652199955</v>
       </c>
       <c r="U83">
         <v>0.0641</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.068859137807778</v>
+        <v>3.031434026371097</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08923195919887994</v>
+        <v>0.09397949706303442</v>
       </c>
       <c r="C84">
-        <v>170.7404201489057</v>
+        <v>106.6535594087779</v>
       </c>
       <c r="D84">
-        <v>763.4804201489059</v>
+        <v>708.913559408778</v>
       </c>
       <c r="E84">
-        <v>125.8400000000001</v>
+        <v>135.3600000000001</v>
       </c>
       <c r="F84">
-        <v>780.6400000000001</v>
+        <v>790.1600000000001</v>
       </c>
       <c r="G84">
         <v>187.9</v>
@@ -8169,45 +8169,45 @@
         <v>151.69</v>
       </c>
       <c r="M84">
-        <v>50.03902400000001</v>
+        <v>56.81250400000001</v>
       </c>
       <c r="N84">
-        <v>101.650976</v>
+        <v>94.87749599999998</v>
       </c>
       <c r="O84">
-        <v>25.412744</v>
+        <v>23.71937399999999</v>
       </c>
       <c r="P84">
-        <v>76.23823199999998</v>
+        <v>71.15812199999999</v>
       </c>
       <c r="Q84">
-        <v>82.04823199999998</v>
+        <v>76.96812199999999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2767247733271109</v>
+        <v>0.2895396886060849</v>
       </c>
       <c r="T84">
-        <v>4.501153652199955</v>
+        <v>4.750940203376424</v>
       </c>
       <c r="U84">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V84">
         <v>0.25</v>
       </c>
       <c r="W84">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y84">
-        <v>3.031434026371097</v>
+        <v>2.670010813112549</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09397949706303442</v>
+        <v>0.09393003492718888</v>
       </c>
       <c r="C85">
-        <v>106.6535594087779</v>
+        <v>97.66182495030841</v>
       </c>
       <c r="D85">
-        <v>708.913559408778</v>
+        <v>709.4418249503085</v>
       </c>
       <c r="E85">
-        <v>135.3600000000001</v>
+        <v>144.8800000000001</v>
       </c>
       <c r="F85">
-        <v>790.1600000000001</v>
+        <v>799.6800000000001</v>
       </c>
       <c r="G85">
         <v>187.9</v>
@@ -8251,28 +8251,28 @@
         <v>151.69</v>
       </c>
       <c r="M85">
-        <v>56.81250400000001</v>
+        <v>57.49699200000001</v>
       </c>
       <c r="N85">
-        <v>94.87749599999998</v>
+        <v>94.19300799999999</v>
       </c>
       <c r="O85">
-        <v>23.71937399999999</v>
+        <v>23.548252</v>
       </c>
       <c r="P85">
-        <v>71.15812199999999</v>
+        <v>70.644756</v>
       </c>
       <c r="Q85">
-        <v>76.96812199999999</v>
+        <v>76.454756</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2895396886060849</v>
+        <v>0.3039564682949307</v>
       </c>
       <c r="T85">
-        <v>4.750940203376424</v>
+        <v>5.031950073449951</v>
       </c>
       <c r="U85">
         <v>0.07190000000000001</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.670010813112549</v>
+        <v>2.638224970099305</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09393003492718888</v>
+        <v>0.09388057279134335</v>
       </c>
       <c r="C86">
-        <v>97.66182495030853</v>
+        <v>88.67087838081636</v>
       </c>
       <c r="D86">
-        <v>709.4418249503085</v>
+        <v>709.9708783808163</v>
       </c>
       <c r="E86">
-        <v>144.88</v>
+        <v>154.4</v>
       </c>
       <c r="F86">
-        <v>799.6799999999999</v>
+        <v>809.1999999999999</v>
       </c>
       <c r="G86">
         <v>187.9</v>
@@ -8333,28 +8333,28 @@
         <v>151.69</v>
       </c>
       <c r="M86">
-        <v>57.496992</v>
+        <v>58.18148</v>
       </c>
       <c r="N86">
-        <v>94.19300799999999</v>
+        <v>93.50852</v>
       </c>
       <c r="O86">
-        <v>23.548252</v>
+        <v>23.37713</v>
       </c>
       <c r="P86">
-        <v>70.644756</v>
+        <v>70.13139000000001</v>
       </c>
       <c r="Q86">
-        <v>76.454756</v>
+        <v>75.94139000000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3039564682949305</v>
+        <v>0.3202954852756223</v>
       </c>
       <c r="T86">
-        <v>5.031950073449948</v>
+        <v>5.350427926199945</v>
       </c>
       <c r="U86">
         <v>0.07190000000000001</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.638224970099305</v>
+        <v>2.607187029274608</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09388057279134335</v>
+        <v>0.09383111065549782</v>
       </c>
       <c r="C87">
-        <v>88.67087838081636</v>
+        <v>79.68072146427869</v>
       </c>
       <c r="D87">
-        <v>709.9708783808163</v>
+        <v>710.5007214642787</v>
       </c>
       <c r="E87">
-        <v>154.4</v>
+        <v>163.9200000000001</v>
       </c>
       <c r="F87">
-        <v>809.1999999999999</v>
+        <v>818.72</v>
       </c>
       <c r="G87">
         <v>187.9</v>
@@ -8415,28 +8415,28 @@
         <v>151.69</v>
       </c>
       <c r="M87">
-        <v>58.18148</v>
+        <v>58.86596800000001</v>
       </c>
       <c r="N87">
-        <v>93.50852</v>
+        <v>92.82403199999999</v>
       </c>
       <c r="O87">
-        <v>23.37713</v>
+        <v>23.206008</v>
       </c>
       <c r="P87">
-        <v>70.13139000000001</v>
+        <v>69.61802399999999</v>
       </c>
       <c r="Q87">
-        <v>75.94139000000001</v>
+        <v>75.42802399999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3202954852756223</v>
+        <v>0.33896864753927</v>
       </c>
       <c r="T87">
-        <v>5.350427926199945</v>
+        <v>5.714402615057083</v>
       </c>
       <c r="U87">
         <v>0.07190000000000001</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.607187029274608</v>
+        <v>2.576870901027228</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09383111065549782</v>
+        <v>0.09378164851965226</v>
       </c>
       <c r="C88">
-        <v>79.68072146427869</v>
+        <v>70.69135596994329</v>
       </c>
       <c r="D88">
-        <v>710.5007214642787</v>
+        <v>711.0313559699433</v>
       </c>
       <c r="E88">
-        <v>163.9200000000001</v>
+        <v>173.4400000000001</v>
       </c>
       <c r="F88">
-        <v>818.72</v>
+        <v>828.24</v>
       </c>
       <c r="G88">
         <v>187.9</v>
@@ -8497,28 +8497,28 @@
         <v>151.69</v>
       </c>
       <c r="M88">
-        <v>58.86596800000001</v>
+        <v>59.550456</v>
       </c>
       <c r="N88">
-        <v>92.82403199999999</v>
+        <v>92.139544</v>
       </c>
       <c r="O88">
-        <v>23.206008</v>
+        <v>23.034886</v>
       </c>
       <c r="P88">
-        <v>69.61802399999999</v>
+        <v>69.104658</v>
       </c>
       <c r="Q88">
-        <v>75.42802399999999</v>
+        <v>74.914658</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.33896864753927</v>
+        <v>0.3605146039973252</v>
       </c>
       <c r="T88">
-        <v>5.714402615057083</v>
+        <v>6.134373409892244</v>
       </c>
       <c r="U88">
         <v>0.07190000000000001</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.576870901027228</v>
+        <v>2.547251695268295</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09378164851965226</v>
+        <v>0.09373218638380676</v>
       </c>
       <c r="C89">
-        <v>70.69135596994329</v>
+        <v>61.70278367234539</v>
       </c>
       <c r="D89">
-        <v>711.0313559699433</v>
+        <v>711.5627836723454</v>
       </c>
       <c r="E89">
-        <v>173.4400000000001</v>
+        <v>182.96</v>
       </c>
       <c r="F89">
-        <v>828.24</v>
+        <v>837.76</v>
       </c>
       <c r="G89">
         <v>187.9</v>
@@ -8579,28 +8579,28 @@
         <v>151.69</v>
       </c>
       <c r="M89">
-        <v>59.550456</v>
+        <v>60.23494400000001</v>
       </c>
       <c r="N89">
-        <v>92.139544</v>
+        <v>91.45505599999998</v>
       </c>
       <c r="O89">
-        <v>23.034886</v>
+        <v>22.863764</v>
       </c>
       <c r="P89">
-        <v>69.104658</v>
+        <v>68.59129199999998</v>
       </c>
       <c r="Q89">
-        <v>74.914658</v>
+        <v>74.40129199999998</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3605146039973252</v>
+        <v>0.3856515531983896</v>
       </c>
       <c r="T89">
-        <v>6.134373409892244</v>
+        <v>6.624339337199932</v>
       </c>
       <c r="U89">
         <v>0.07190000000000001</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.547251695268295</v>
+        <v>2.518305653276609</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.09373218638380676</v>
+        <v>0.0962859742479612</v>
       </c>
       <c r="C90">
-        <v>61.70278367234539</v>
+        <v>25.74428726072369</v>
       </c>
       <c r="D90">
-        <v>711.5627836723454</v>
+        <v>685.1242872607237</v>
       </c>
       <c r="E90">
-        <v>182.96</v>
+        <v>192.48</v>
       </c>
       <c r="F90">
-        <v>837.76</v>
+        <v>847.28</v>
       </c>
       <c r="G90">
         <v>187.9</v>
@@ -8661,45 +8661,45 @@
         <v>151.69</v>
       </c>
       <c r="M90">
-        <v>60.23494400000001</v>
+        <v>64.22382400000001</v>
       </c>
       <c r="N90">
-        <v>91.45505599999998</v>
+        <v>87.46617599999999</v>
       </c>
       <c r="O90">
-        <v>22.863764</v>
+        <v>21.866544</v>
       </c>
       <c r="P90">
-        <v>68.59129199999998</v>
+        <v>65.59963199999999</v>
       </c>
       <c r="Q90">
-        <v>74.40129199999998</v>
+        <v>71.40963199999999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3856515531983896</v>
+        <v>0.4153588567996473</v>
       </c>
       <c r="T90">
-        <v>6.624339337199932</v>
+        <v>7.203389978563562</v>
       </c>
       <c r="U90">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V90">
         <v>0.25</v>
       </c>
       <c r="W90">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y90">
-        <v>2.518305653276609</v>
+        <v>2.361896108833382</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.0962859742479612</v>
+        <v>0.09626576211211568</v>
       </c>
       <c r="C91">
-        <v>25.74428726072369</v>
+        <v>16.42582111558249</v>
       </c>
       <c r="D91">
-        <v>685.1242872607237</v>
+        <v>685.3258211155826</v>
       </c>
       <c r="E91">
-        <v>192.48</v>
+        <v>202.0000000000001</v>
       </c>
       <c r="F91">
-        <v>847.28</v>
+        <v>856.8000000000001</v>
       </c>
       <c r="G91">
         <v>187.9</v>
@@ -8743,28 +8743,28 @@
         <v>151.69</v>
       </c>
       <c r="M91">
-        <v>64.22382400000001</v>
+        <v>64.94544</v>
       </c>
       <c r="N91">
-        <v>87.46617599999999</v>
+        <v>86.74455999999999</v>
       </c>
       <c r="O91">
-        <v>21.866544</v>
+        <v>21.68614</v>
       </c>
       <c r="P91">
-        <v>65.59963199999999</v>
+        <v>65.05842</v>
       </c>
       <c r="Q91">
-        <v>71.40963199999999</v>
+        <v>70.86842</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4153588567996473</v>
+        <v>0.4510076211211568</v>
       </c>
       <c r="T91">
-        <v>7.203389978563562</v>
+        <v>7.898250748199921</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.361896108833382</v>
+        <v>2.335652818735233</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.09626576211211568</v>
+        <v>0.09624554997627015</v>
       </c>
       <c r="C92">
-        <v>16.42582111558249</v>
+        <v>7.107473570369621</v>
       </c>
       <c r="D92">
-        <v>685.3258211155826</v>
+        <v>685.5274735703697</v>
       </c>
       <c r="E92">
-        <v>202.0000000000001</v>
+        <v>211.5200000000001</v>
       </c>
       <c r="F92">
-        <v>856.8000000000001</v>
+        <v>866.3200000000001</v>
       </c>
       <c r="G92">
         <v>187.9</v>
@@ -8825,28 +8825,28 @@
         <v>151.69</v>
       </c>
       <c r="M92">
-        <v>64.94544</v>
+        <v>65.667056</v>
       </c>
       <c r="N92">
-        <v>86.74455999999999</v>
+        <v>86.022944</v>
       </c>
       <c r="O92">
-        <v>21.68614</v>
+        <v>21.505736</v>
       </c>
       <c r="P92">
-        <v>65.05842</v>
+        <v>64.517208</v>
       </c>
       <c r="Q92">
-        <v>70.86842</v>
+        <v>70.327208</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4510076211211568</v>
+        <v>0.4945783330696684</v>
       </c>
       <c r="T92">
-        <v>7.898250748199921</v>
+        <v>8.747525022199913</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.335652818735233</v>
+        <v>2.309986304243638</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.09624554997627015</v>
+        <v>0.09622533784042461</v>
       </c>
       <c r="C93">
-        <v>7.107473570369621</v>
+        <v>-2.210755270192635</v>
       </c>
       <c r="D93">
-        <v>685.5274735703697</v>
+        <v>685.7292447298074</v>
       </c>
       <c r="E93">
-        <v>211.5200000000001</v>
+        <v>221.0400000000001</v>
       </c>
       <c r="F93">
-        <v>866.3200000000001</v>
+        <v>875.84</v>
       </c>
       <c r="G93">
         <v>187.9</v>
@@ -8907,28 +8907,28 @@
         <v>151.69</v>
       </c>
       <c r="M93">
-        <v>65.667056</v>
+        <v>66.38867200000001</v>
       </c>
       <c r="N93">
-        <v>86.022944</v>
+        <v>85.30132799999998</v>
       </c>
       <c r="O93">
-        <v>21.505736</v>
+        <v>21.325332</v>
       </c>
       <c r="P93">
-        <v>64.517208</v>
+        <v>63.97599599999999</v>
       </c>
       <c r="Q93">
-        <v>70.327208</v>
+        <v>69.78599599999998</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4945783330696684</v>
+        <v>0.5490417230053078</v>
       </c>
       <c r="T93">
-        <v>8.747525022199913</v>
+        <v>9.809117864699905</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.309986304243638</v>
+        <v>2.28487775745838</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.09622533784042461</v>
+        <v>0.09620512570457906</v>
       </c>
       <c r="C94">
-        <v>-2.210755270192635</v>
+        <v>-11.52886530125841</v>
       </c>
       <c r="D94">
-        <v>685.7292447298074</v>
+        <v>685.9311346987416</v>
       </c>
       <c r="E94">
-        <v>221.0400000000001</v>
+        <v>230.5600000000001</v>
       </c>
       <c r="F94">
-        <v>875.84</v>
+        <v>885.36</v>
       </c>
       <c r="G94">
         <v>187.9</v>
@@ -8989,28 +8989,28 @@
         <v>151.69</v>
       </c>
       <c r="M94">
-        <v>66.38867200000001</v>
+        <v>67.11028800000001</v>
       </c>
       <c r="N94">
-        <v>85.30132799999998</v>
+        <v>84.57971199999999</v>
       </c>
       <c r="O94">
-        <v>21.325332</v>
+        <v>21.144928</v>
       </c>
       <c r="P94">
-        <v>63.97599599999999</v>
+        <v>63.43478399999999</v>
       </c>
       <c r="Q94">
-        <v>69.78599599999998</v>
+        <v>69.244784</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5490417230053078</v>
+        <v>0.619066081493987</v>
       </c>
       <c r="T94">
-        <v>9.809117864699905</v>
+        <v>11.17402294791418</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.28487775745838</v>
+        <v>2.260309179421194</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.09620512570457906</v>
+        <v>0.09618491356873353</v>
       </c>
       <c r="C95">
-        <v>-11.52886530125841</v>
+        <v>-20.84685641785882</v>
       </c>
       <c r="D95">
-        <v>685.9311346987416</v>
+        <v>686.1331435821413</v>
       </c>
       <c r="E95">
-        <v>230.5600000000001</v>
+        <v>240.0800000000002</v>
       </c>
       <c r="F95">
-        <v>885.36</v>
+        <v>894.8800000000001</v>
       </c>
       <c r="G95">
         <v>187.9</v>
@@ -9071,28 +9071,28 @@
         <v>151.69</v>
       </c>
       <c r="M95">
-        <v>67.11028800000001</v>
+        <v>67.83190400000001</v>
       </c>
       <c r="N95">
-        <v>84.57971199999999</v>
+        <v>83.85809599999999</v>
       </c>
       <c r="O95">
-        <v>21.144928</v>
+        <v>20.964524</v>
       </c>
       <c r="P95">
-        <v>63.43478399999999</v>
+        <v>62.89357199999999</v>
       </c>
       <c r="Q95">
-        <v>69.244784</v>
+        <v>68.70357199999999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.619066081493987</v>
+        <v>0.7124318928122261</v>
       </c>
       <c r="T95">
-        <v>11.17402294791418</v>
+        <v>12.99389639219988</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.260309179421194</v>
+        <v>2.236263337086926</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09618491356873353</v>
+        <v>0.09616470143288801</v>
       </c>
       <c r="C96">
-        <v>-20.84685641785882</v>
+        <v>-30.16472851490039</v>
       </c>
       <c r="D96">
-        <v>686.1331435821413</v>
+        <v>686.3352714850997</v>
       </c>
       <c r="E96">
-        <v>240.0800000000002</v>
+        <v>249.6000000000001</v>
       </c>
       <c r="F96">
-        <v>894.8800000000001</v>
+        <v>904.4000000000001</v>
       </c>
       <c r="G96">
         <v>187.9</v>
@@ -9153,28 +9153,28 @@
         <v>151.69</v>
       </c>
       <c r="M96">
-        <v>67.83190400000001</v>
+        <v>68.55352000000001</v>
       </c>
       <c r="N96">
-        <v>83.85809599999999</v>
+        <v>83.13647999999999</v>
       </c>
       <c r="O96">
-        <v>20.964524</v>
+        <v>20.78412</v>
       </c>
       <c r="P96">
-        <v>62.89357199999999</v>
+        <v>62.35235999999999</v>
       </c>
       <c r="Q96">
-        <v>68.70357199999999</v>
+        <v>68.16235999999999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7124318928122261</v>
+        <v>0.8431440286577612</v>
       </c>
       <c r="T96">
-        <v>12.99389639219988</v>
+        <v>15.54171921419986</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.236263337086926</v>
+        <v>2.212723723012326</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.09616470143288801</v>
+        <v>0.09614448929704247</v>
       </c>
       <c r="C97">
-        <v>-30.16472851490039</v>
+        <v>-39.4824814871663</v>
       </c>
       <c r="D97">
-        <v>686.3352714850997</v>
+        <v>686.5375185128338</v>
       </c>
       <c r="E97">
-        <v>249.6000000000001</v>
+        <v>259.1200000000001</v>
       </c>
       <c r="F97">
-        <v>904.4000000000001</v>
+        <v>913.9200000000001</v>
       </c>
       <c r="G97">
         <v>187.9</v>
@@ -9235,28 +9235,28 @@
         <v>151.69</v>
       </c>
       <c r="M97">
-        <v>68.55352000000001</v>
+        <v>69.27513600000002</v>
       </c>
       <c r="N97">
-        <v>83.13647999999999</v>
+        <v>82.41486399999998</v>
       </c>
       <c r="O97">
-        <v>20.78412</v>
+        <v>20.603716</v>
       </c>
       <c r="P97">
-        <v>62.35235999999999</v>
+        <v>61.81114799999999</v>
       </c>
       <c r="Q97">
-        <v>68.16235999999999</v>
+        <v>67.62114799999999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8431440286577612</v>
+        <v>1.039212232426064</v>
       </c>
       <c r="T97">
-        <v>15.54171921419986</v>
+        <v>19.36345344719984</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.212723723012326</v>
+        <v>2.189674517564281</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.09614448929704247</v>
+        <v>0.09612427716119695</v>
       </c>
       <c r="C98">
-        <v>-39.48248148716618</v>
+        <v>-48.80011522931579</v>
       </c>
       <c r="D98">
-        <v>686.5375185128338</v>
+        <v>686.7398847706842</v>
       </c>
       <c r="E98">
-        <v>259.12</v>
+        <v>268.64</v>
       </c>
       <c r="F98">
-        <v>913.92</v>
+        <v>923.4399999999999</v>
       </c>
       <c r="G98">
         <v>187.9</v>
@@ -9317,28 +9317,28 @@
         <v>151.69</v>
       </c>
       <c r="M98">
-        <v>69.275136</v>
+        <v>69.996752</v>
       </c>
       <c r="N98">
-        <v>82.41486399999999</v>
+        <v>81.693248</v>
       </c>
       <c r="O98">
-        <v>20.603716</v>
+        <v>20.423312</v>
       </c>
       <c r="P98">
-        <v>61.811148</v>
+        <v>61.269936</v>
       </c>
       <c r="Q98">
-        <v>67.62114799999999</v>
+        <v>67.079936</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.039212232426061</v>
+        <v>1.365992572039897</v>
       </c>
       <c r="T98">
-        <v>19.36345344719978</v>
+        <v>25.73301050219971</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.189674517564281</v>
+        <v>2.167100553465681</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.09612427716119695</v>
+        <v>0.0961040650253514</v>
       </c>
       <c r="C99">
-        <v>-48.80011522931579</v>
+        <v>-58.11762963588342</v>
       </c>
       <c r="D99">
-        <v>686.7398847706842</v>
+        <v>686.9423703641166</v>
       </c>
       <c r="E99">
-        <v>268.64</v>
+        <v>278.1600000000001</v>
       </c>
       <c r="F99">
-        <v>923.4399999999999</v>
+        <v>932.96</v>
       </c>
       <c r="G99">
         <v>187.9</v>
@@ -9399,28 +9399,28 @@
         <v>151.69</v>
       </c>
       <c r="M99">
-        <v>69.996752</v>
+        <v>70.71836800000001</v>
       </c>
       <c r="N99">
-        <v>81.693248</v>
+        <v>80.97163199999999</v>
       </c>
       <c r="O99">
-        <v>20.423312</v>
+        <v>20.242908</v>
       </c>
       <c r="P99">
-        <v>61.269936</v>
+        <v>60.72872399999999</v>
       </c>
       <c r="Q99">
-        <v>67.079936</v>
+        <v>66.53872399999999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.365992572039897</v>
+        <v>2.019553251267568</v>
       </c>
       <c r="T99">
-        <v>25.73301050219971</v>
+        <v>38.47212461219957</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.167100553465681</v>
+        <v>2.144987282511949</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.0961040650253514</v>
+        <v>0.09608385288950587</v>
       </c>
       <c r="C100">
-        <v>-58.11762963588342</v>
+        <v>-67.43502460127991</v>
       </c>
       <c r="D100">
-        <v>686.9423703641166</v>
+        <v>687.1449753987201</v>
       </c>
       <c r="E100">
-        <v>278.1600000000001</v>
+        <v>287.6800000000001</v>
       </c>
       <c r="F100">
-        <v>932.96</v>
+        <v>942.48</v>
       </c>
       <c r="G100">
         <v>187.9</v>
@@ -9481,28 +9481,28 @@
         <v>151.69</v>
       </c>
       <c r="M100">
-        <v>70.71836800000001</v>
+        <v>71.43998400000001</v>
       </c>
       <c r="N100">
-        <v>80.97163199999999</v>
+        <v>80.25001599999999</v>
       </c>
       <c r="O100">
-        <v>20.242908</v>
+        <v>20.062504</v>
       </c>
       <c r="P100">
-        <v>60.72872399999999</v>
+        <v>60.18751199999999</v>
       </c>
       <c r="Q100">
-        <v>66.53872399999999</v>
+        <v>65.99751199999999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.019553251267568</v>
+        <v>3.980235288950583</v>
       </c>
       <c r="T100">
-        <v>38.47212461219957</v>
+        <v>76.68946694219915</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.144987282511949</v>
+        <v>2.123320744304758</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.09608385288950587</v>
-      </c>
-      <c r="C101">
-        <v>-67.43502460127991</v>
-      </c>
-      <c r="D101">
-        <v>687.1449753987201</v>
-      </c>
-      <c r="E101">
-        <v>287.6800000000001</v>
-      </c>
-      <c r="F101">
-        <v>942.48</v>
-      </c>
-      <c r="G101">
-        <v>187.9</v>
-      </c>
-      <c r="H101">
-        <v>297.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>157.5</v>
-      </c>
-      <c r="K101">
-        <v>5.81</v>
-      </c>
-      <c r="L101">
-        <v>151.69</v>
-      </c>
-      <c r="M101">
-        <v>71.43998400000001</v>
-      </c>
-      <c r="N101">
-        <v>80.25001599999999</v>
-      </c>
-      <c r="O101">
-        <v>20.062504</v>
-      </c>
-      <c r="P101">
-        <v>60.18751199999999</v>
-      </c>
-      <c r="Q101">
-        <v>65.99751199999999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.980235288950583</v>
-      </c>
-      <c r="T101">
-        <v>76.68946694219915</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.25</v>
-      </c>
-      <c r="W101">
-        <v>0.05685</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.123320744304758</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
